--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
   <si>
     <t>Desis</t>
   </si>
@@ -78,15 +78,9 @@
     <t>sliding + sliding</t>
   </si>
   <si>
-    <t>punctuation + unctuation</t>
-  </si>
-  <si>
     <t>sliding + punctuation</t>
   </si>
   <si>
-    <t>end randomly</t>
-  </si>
-  <si>
     <t>Mix Aggregation Functions</t>
   </si>
   <si>
@@ -109,6 +103,15 @@
   </si>
   <si>
     <t>Mix Window Measure</t>
+  </si>
+  <si>
+    <t>punctuation + punctuation</t>
+  </si>
+  <si>
+    <t>random size</t>
+  </si>
+  <si>
+    <t>thread</t>
   </si>
 </sst>
 </file>
@@ -150,15 +153,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -171,6 +168,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -478,42 +484,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S69"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.77734375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="9.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="1"/>
+    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.90625" style="1"/>
+    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
+    <col min="7" max="9" width="8.90625" style="1"/>
+    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.81640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.90625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -536,30 +542,33 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B4" s="5">
+        <v>16657760</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -584,111 +593,131 @@
       <c r="I9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="D10" s="5">
+        <v>16657760</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1.7392266270315</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="4">
+        <v>1.7392266270315</v>
+      </c>
+      <c r="M10" s="3">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K11" s="3"/>
+      <c r="L11" s="4">
+        <v>1.5392266270315</v>
+      </c>
+      <c r="M11" s="3">
+        <v>2</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="K12" s="3"/>
+      <c r="L12" s="4">
+        <v>11518356.643356601</v>
+      </c>
+      <c r="M12" s="6">
+        <v>4</v>
+      </c>
+      <c r="N12" s="4"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B18" s="1">
         <v>1</v>
       </c>
@@ -717,51 +746,51 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>16210306</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>13825719</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5">
         <v>12683639</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>16142883</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>1383279</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7">
+      <c r="D20" s="5"/>
+      <c r="E20" s="5">
         <v>12782692</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B24" s="1">
         <v>1</v>
       </c>
@@ -787,33 +816,33 @@
         <v>10</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B30" s="1">
         <v>1</v>
       </c>
@@ -839,48 +868,48 @@
         <v>10</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B39" s="1">
         <v>1</v>
       </c>
@@ -903,56 +932,56 @@
         <v>1000</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>16657760</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="5">
         <v>13688831</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7">
+      <c r="D40" s="5"/>
+      <c r="E40" s="5">
         <v>12696323</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="5">
         <v>16767132</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="5">
         <v>9983241</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7">
+      <c r="D41" s="5"/>
+      <c r="E41" s="5">
         <v>9309745</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -975,36 +1004,36 @@
         <v>1000</v>
       </c>
       <c r="J45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1027,36 +1056,36 @@
         <v>1000</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A56" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1079,129 +1108,129 @@
         <v>1000</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A64" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4">
-        <v>1</v>
-      </c>
-      <c r="C66" s="4">
-        <v>10</v>
-      </c>
-      <c r="D66" s="4">
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A65" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2">
+        <v>1</v>
+      </c>
+      <c r="C66" s="2">
+        <v>10</v>
+      </c>
+      <c r="D66" s="2">
         <v>50</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="2">
         <v>100</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="2">
         <v>200</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G66" s="2">
         <v>500</v>
       </c>
-      <c r="H66" s="4">
+      <c r="H66" s="2">
         <v>1000</v>
       </c>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="4" t="s">
+      <c r="I66" s="2"/>
+      <c r="J66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1227,7 +1256,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1236,7 +1265,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -878,6 +878,9 @@
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -1234,6 +1237,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A16:G16"/>
@@ -1241,13 +1251,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A56:D56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
   <si>
     <t>Desis</t>
   </si>
@@ -484,23 +484,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S69"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.77734375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="9.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="1"/>
+    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.90625" style="1"/>
+    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
+    <col min="7" max="9" width="8.90625" style="1"/>
+    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.81640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.90625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
@@ -511,7 +511,7 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
@@ -519,7 +519,7 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -542,7 +542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,17 +550,17 @@
         <v>16657760</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -568,7 +568,7 @@
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -605,7 +605,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,7 +629,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -647,7 +647,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -665,7 +665,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -676,7 +676,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -687,7 +687,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -698,7 +698,7 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
@@ -709,7 +709,7 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
@@ -717,7 +717,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B18" s="1">
         <v>1</v>
       </c>
@@ -746,7 +746,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,7 +761,7 @@
         <v>12683639</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
@@ -776,13 +776,13 @@
         <v>12782692</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>18</v>
       </c>
@@ -790,7 +790,7 @@
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B24" s="1">
         <v>1</v>
       </c>
@@ -819,22 +819,22 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>18</v>
       </c>
@@ -842,7 +842,7 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B30" s="1">
         <v>1</v>
       </c>
@@ -874,7 +874,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,17 +882,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>17</v>
       </c>
@@ -904,7 +904,7 @@
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>21</v>
       </c>
@@ -912,7 +912,7 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B39" s="1">
         <v>1</v>
       </c>
@@ -940,8 +940,11 @@
       <c r="K39" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -956,7 +959,7 @@
         <v>12696323</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
@@ -971,12 +974,12 @@
         <v>9309745</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>21</v>
       </c>
@@ -984,7 +987,7 @@
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -1013,22 +1016,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>21</v>
       </c>
@@ -1036,7 +1039,7 @@
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1065,22 +1068,22 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
         <v>21</v>
       </c>
@@ -1088,7 +1091,7 @@
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1117,22 +1120,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>17</v>
       </c>
@@ -1144,7 +1147,7 @@
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>28</v>
       </c>
@@ -1159,7 +1162,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="2"/>
       <c r="B66" s="2">
         <v>1</v>
@@ -1190,7 +1193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>0</v>
       </c>
@@ -1205,7 +1208,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>2</v>
       </c>
@@ -1220,7 +1223,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>1</v>
       </c>
@@ -1237,6 +1240,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A64:H64"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A65:D65"/>
@@ -1244,13 +1254,6 @@
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1259,7 +1262,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1268,7 +1271,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="33">
   <si>
     <t>Desis</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Mix Window Type</t>
   </si>
   <si>
-    <t>sliding + sliding</t>
-  </si>
-  <si>
     <t>sliding + punctuation</t>
   </si>
   <si>
@@ -112,6 +109,12 @@
   </si>
   <si>
     <t>thread</t>
+  </si>
+  <si>
+    <t>tumling tumbling</t>
+  </si>
+  <si>
+    <t>quantile</t>
   </si>
 </sst>
 </file>
@@ -127,7 +130,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,8 +143,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -149,11 +158,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -176,7 +200,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -483,43 +516,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S69"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S76"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="1"/>
-    <col min="2" max="2" width="9.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="1"/>
-    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" style="1"/>
-    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.90625" style="1"/>
-    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.81640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.77734375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -542,7 +575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,25 +583,25 @@
         <v>16657760</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -596,7 +629,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -605,7 +638,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,7 +662,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -647,7 +680,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -665,7 +698,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -676,7 +709,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -687,7 +720,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -698,183 +731,193 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B18" s="1">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B18" s="10">
+        <v>1</v>
+      </c>
+      <c r="C18" s="10">
         <v>10</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="10">
         <v>50</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="10">
         <v>100</v>
       </c>
-      <c r="F18" s="1">
-        <v>200</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="F18" s="10">
         <v>500</v>
       </c>
-      <c r="H18" s="1">
+      <c r="G18" s="10">
         <v>1000</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="5">
-        <v>16210306</v>
-      </c>
-      <c r="C19" s="5">
-        <v>13825719</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5">
-        <v>12683639</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B19" s="11">
+        <v>30545075.399999999</v>
+      </c>
+      <c r="C19" s="11">
+        <v>30170030.661380101</v>
+      </c>
+      <c r="D19" s="11">
+        <v>29975328.866937201</v>
+      </c>
+      <c r="E19" s="11">
+        <v>29993363.038345698</v>
+      </c>
+      <c r="F19" s="11">
+        <v>30042764.404131401</v>
+      </c>
+      <c r="G19" s="11">
+        <v>30084216.821240999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="5">
-        <v>16142883</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1383279</v>
-      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5">
-        <v>12782692</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
+      <c r="B21" s="11">
+        <v>3200594.9</v>
+      </c>
+      <c r="C21" s="11">
+        <v>843380.47</v>
+      </c>
+      <c r="D21" s="11">
+        <v>244432.04</v>
+      </c>
+      <c r="E21" s="11">
+        <v>142866.29999999999</v>
+      </c>
+      <c r="F21" s="11">
+        <v>57506.04</v>
+      </c>
+      <c r="G21" s="11">
+        <v>48292.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="10">
         <v>10</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="10">
         <v>50</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="10">
         <v>100</v>
       </c>
-      <c r="F24" s="1">
-        <v>200</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="F24" s="10">
         <v>500</v>
       </c>
-      <c r="H24" s="1">
+      <c r="G24" s="10">
         <v>1000</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B30" s="1">
-        <v>1</v>
-      </c>
-      <c r="C30" s="1">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="10">
+        <v>2</v>
+      </c>
+      <c r="C30" s="10">
         <v>10</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="10">
         <v>50</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="10">
         <v>100</v>
       </c>
-      <c r="F30" s="1">
-        <v>200</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="F30" s="10">
         <v>500</v>
       </c>
-      <c r="H30" s="1">
+      <c r="G30" s="10">
         <v>1000</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,37 +925,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
         <v>1</v>
       </c>
@@ -935,16 +978,16 @@
         <v>1000</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,7 +1002,7 @@
         <v>12696323</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
@@ -974,20 +1017,20 @@
         <v>9309745</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -1010,36 +1053,36 @@
         <v>1000</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1062,36 +1105,36 @@
         <v>1000</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A56" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1114,30 +1157,76 @@
         <v>1000</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7">
+        <v>1</v>
+      </c>
+      <c r="C63" s="7">
+        <v>10</v>
+      </c>
+      <c r="D63" s="7">
+        <v>50</v>
+      </c>
+      <c r="E63" s="7">
+        <v>100</v>
+      </c>
+      <c r="F63" s="7">
+        <v>200</v>
+      </c>
+      <c r="G63" s="7">
+        <v>500</v>
+      </c>
+      <c r="H63" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -1146,100 +1235,153 @@
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2">
-        <v>1</v>
-      </c>
-      <c r="C66" s="2">
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2">
+        <v>1</v>
+      </c>
+      <c r="C73" s="2">
         <v>10</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D73" s="2">
         <v>50</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E73" s="2">
         <v>100</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F73" s="2">
         <v>200</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G73" s="2">
         <v>500</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H73" s="2">
         <v>1000</v>
       </c>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2" t="s">
+      <c r="I73" s="2"/>
+      <c r="J73" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K66" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
+      <c r="K73" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A68" s="2" t="s">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A69" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A16:G16"/>
@@ -1247,13 +1389,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A56:D56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1262,7 +1397,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1271,7 +1406,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView minimized="1" xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -200,16 +200,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -517,42 +523,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.77734375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="9.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="1"/>
+    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.90625" style="1"/>
+    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="1"/>
+    <col min="8" max="8" width="29.90625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.90625" style="1"/>
+    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.81640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.90625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -575,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,25 +591,25 @@
         <v>16657760</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -638,7 +646,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,7 +670,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -680,7 +688,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -698,7 +706,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -709,7 +717,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -720,7 +728,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -731,42 +739,42 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B18" s="10">
-        <v>1</v>
-      </c>
-      <c r="C18" s="10">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8">
         <v>10</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <v>50</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="8">
         <v>100</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="8">
         <v>500</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="8">
         <v>1000</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -776,30 +784,30 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>30545075.399999999</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="9">
         <v>30170030.661380101</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="9">
         <v>29975328.866937201</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="9">
         <v>29993363.038345698</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="9">
         <v>30042764.404131401</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="9">
         <v>30084216.821240999</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
@@ -808,54 +816,54 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>3200594.9</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="9">
         <v>843380.47</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="9">
         <v>244432.04</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="9">
         <v>142866.29999999999</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="9">
         <v>57506.04</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="9">
         <v>48292.25</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="10">
-        <v>2</v>
-      </c>
-      <c r="C24" s="10">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="8">
+        <v>2</v>
+      </c>
+      <c r="C24" s="8">
         <v>10</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="8">
         <v>50</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="8">
         <v>100</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="8">
         <v>500</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="8">
         <v>1000</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -865,46 +873,46 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="10">
-        <v>2</v>
-      </c>
-      <c r="C30" s="10">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="8">
+        <v>2</v>
+      </c>
+      <c r="C30" s="8">
         <v>10</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="8">
         <v>50</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="8">
         <v>100</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="8">
         <v>500</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="8">
         <v>1000</v>
       </c>
       <c r="J30" s="1" t="s">
@@ -917,7 +925,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -925,39 +933,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="1">
         <v>10</v>
@@ -987,50 +995,42 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="5">
-        <v>16657760</v>
-      </c>
-      <c r="C40" s="5">
-        <v>13688831</v>
-      </c>
+      <c r="B40" s="9">
+        <v>30545075.399999999</v>
+      </c>
+      <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="5">
-        <v>12696323</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B41" s="5">
-        <v>16767132</v>
-      </c>
-      <c r="C41" s="5">
-        <v>9983241</v>
-      </c>
+        <v>29117997.387228101</v>
+      </c>
+      <c r="C41" s="5"/>
       <c r="D41" s="5"/>
-      <c r="E41" s="5">
-        <v>9309745</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -1059,30 +1059,30 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1111,30 +1111,30 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="8" t="s">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A56" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1163,28 +1163,28 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="8" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A62" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -1193,25 +1193,25 @@
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="7"/>
-      <c r="B63" s="7">
-        <v>1</v>
-      </c>
-      <c r="C63" s="7">
+      <c r="B63" s="8">
+        <v>2</v>
+      </c>
+      <c r="C63" s="8">
         <v>10</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="8">
         <v>50</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="8">
         <v>100</v>
       </c>
-      <c r="F63" s="7">
-        <v>200</v>
-      </c>
-      <c r="G63" s="7">
+      <c r="F63" s="8">
         <v>500</v>
+      </c>
+      <c r="G63" s="8">
+        <v>1000</v>
       </c>
       <c r="H63" s="7">
         <v>1000</v>
@@ -1224,70 +1224,97 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
+      <c r="B64" s="12">
+        <v>7057527.2400000002</v>
+      </c>
+      <c r="C64" s="12">
+        <v>7124118.9299999997</v>
+      </c>
+      <c r="D64" s="12">
+        <v>7474829</v>
+      </c>
+      <c r="E64" s="12">
+        <v>7465423.46</v>
+      </c>
+      <c r="F64" s="12">
+        <v>7278250.2000000002</v>
+      </c>
+      <c r="G64" s="12">
+        <v>7336149.25</v>
+      </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
+      <c r="B65" s="12">
+        <v>2910000.75</v>
+      </c>
+      <c r="C65" s="12">
+        <v>869738.37</v>
+      </c>
+      <c r="D65" s="12">
+        <v>486379.3</v>
+      </c>
+      <c r="E65" s="12">
+        <v>203258.57</v>
+      </c>
+      <c r="F65" s="12">
+        <v>53545.05</v>
+      </c>
+      <c r="G65" s="12">
+        <v>13893.87</v>
+      </c>
+      <c r="H65" s="5"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
+      <c r="B66" s="13">
+        <v>1529252</v>
+      </c>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12">
+        <v>46757</v>
+      </c>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="8" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="9" t="s">
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -1296,7 +1323,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2">
         <v>1</v>
@@ -1327,7 +1354,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
@@ -1342,7 +1369,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
@@ -1357,7 +1384,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -1374,6 +1401,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A72:D72"/>
@@ -1382,22 +1416,16 @@
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1406,7 +1434,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
   <si>
     <t>Desis</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Mix Window Type</t>
   </si>
   <si>
-    <t>sliding + punctuation</t>
-  </si>
-  <si>
     <t>Mix Aggregation Functions</t>
   </si>
   <si>
@@ -115,6 +112,21 @@
   </si>
   <si>
     <t>quantile</t>
+  </si>
+  <si>
+    <t>3000l</t>
+  </si>
+  <si>
+    <t>1000s</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>size 1</t>
+  </si>
+  <si>
+    <t>tumbling + punctuation</t>
   </si>
 </sst>
 </file>
@@ -177,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -209,13 +221,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -523,121 +538,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="1"/>
-    <col min="2" max="2" width="9.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="1"/>
-    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.90625" style="1"/>
-    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" style="1"/>
-    <col min="8" max="8" width="29.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.90625" style="1"/>
-    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.81640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5">
-        <v>16657760</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="12">
+        <v>30545075.399999999</v>
+      </c>
+      <c r="C4" s="12">
+        <v>29811997.740027301</v>
+      </c>
+      <c r="D4" s="12">
+        <v>30980630.497990001</v>
+      </c>
+      <c r="E4" s="12">
+        <v>31137398.540112801</v>
+      </c>
+      <c r="F4" s="12">
+        <v>16012225.6874354</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+      <c r="B5" s="12">
+        <v>30635560.517913401</v>
+      </c>
+      <c r="C5" s="12">
+        <v>30094194.446149699</v>
+      </c>
+      <c r="D5" s="12">
+        <v>31055213.250361498</v>
+      </c>
+      <c r="E5" s="12">
+        <v>31169257.825507801</v>
+      </c>
+      <c r="F5" s="12">
+        <v>16001392.5737403</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12">
+        <v>3065244.36</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1463248.92</v>
+      </c>
+      <c r="D6" s="12">
+        <v>2062724.5</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2041280.3995000001</v>
+      </c>
+      <c r="F6" s="12">
+        <v>1937204.07</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -646,15 +739,33 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="5">
-        <v>16657760</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1.7392266270315</v>
+      <c r="B10" s="12">
+        <v>7401292</v>
+      </c>
+      <c r="C10" s="12">
+        <v>7365279.7479999997</v>
+      </c>
+      <c r="D10" s="12">
+        <v>30545075.399999999</v>
+      </c>
+      <c r="E10" s="12">
+        <v>30447031.229639899</v>
+      </c>
+      <c r="F10" s="12">
+        <v>30935064.935064901</v>
+      </c>
+      <c r="G10" s="12">
+        <v>34251061.438561402</v>
+      </c>
+      <c r="H10" s="12">
+        <v>34515041.776405402</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="4">
@@ -670,9 +781,30 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>2</v>
+      </c>
+      <c r="B11" s="12">
+        <v>7387008.6100000003</v>
+      </c>
+      <c r="C11" s="12">
+        <v>7381403.0049999999</v>
+      </c>
+      <c r="D11" s="12">
+        <v>30635560.517913401</v>
+      </c>
+      <c r="E11" s="12">
+        <v>30651978.273827001</v>
+      </c>
+      <c r="F11" s="12">
+        <v>30811652.633081201</v>
+      </c>
+      <c r="G11" s="12">
+        <v>34126088.523348801</v>
+      </c>
+      <c r="H11" s="12">
+        <v>34653452.052534603</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="4">
@@ -688,9 +820,30 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="12">
+        <v>1626861.2661948199</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1622474.0689999999</v>
+      </c>
+      <c r="D12" s="12">
+        <v>3065244.36</v>
+      </c>
+      <c r="E12" s="12">
+        <v>3056406.42</v>
+      </c>
+      <c r="F12" s="12">
+        <v>3104004.67</v>
+      </c>
+      <c r="G12" s="12">
+        <v>3192249.0269999998</v>
+      </c>
+      <c r="H12" s="12">
+        <v>3210081.02</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="4">
@@ -706,7 +859,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -717,7 +870,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -728,7 +881,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -739,28 +892,29 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
       <c r="B18" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="8">
         <v>10</v>
@@ -781,73 +935,87 @@
         <v>10</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="12">
         <v>30545075.399999999</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="12">
         <v>30170030.661380101</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="12">
         <v>29975328.866937201</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="12">
         <v>29993363.038345698</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="12">
         <v>30042764.404131401</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="12">
         <v>30084216.821240999</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="9">
-        <v>3200594.9</v>
-      </c>
-      <c r="C21" s="9">
-        <v>843380.47</v>
-      </c>
-      <c r="D21" s="9">
-        <v>244432.04</v>
-      </c>
-      <c r="E21" s="9">
-        <v>142866.29999999999</v>
-      </c>
-      <c r="F21" s="9">
-        <v>57506.04</v>
-      </c>
-      <c r="G21" s="9">
-        <v>48292.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
+      <c r="B20" s="12">
+        <v>29655883.684660599</v>
+      </c>
+      <c r="C20" s="12">
+        <v>29456607.392607301</v>
+      </c>
+      <c r="D20" s="12">
+        <v>29233313.449140701</v>
+      </c>
+      <c r="E20" s="12">
+        <v>29137664.6609204</v>
+      </c>
+      <c r="F20" s="12">
+        <v>29233253.472191501</v>
+      </c>
+      <c r="G20" s="12">
+        <v>29070066.6240234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="12">
+        <v>2673205.9300000002</v>
+      </c>
+      <c r="C21" s="12">
+        <v>876913.8</v>
+      </c>
+      <c r="D21" s="12">
+        <v>362475.64</v>
+      </c>
+      <c r="E21" s="12">
+        <v>223458.038</v>
+      </c>
+      <c r="F21" s="12">
+        <v>154271.15</v>
+      </c>
+      <c r="G21" s="12">
+        <v>129632.158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <v>2</v>
       </c>
@@ -870,33 +1038,33 @@
         <v>10</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <v>2</v>
       </c>
@@ -919,13 +1087,13 @@
         <v>10</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -933,37 +1101,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
         <v>2</v>
       </c>
@@ -986,16 +1154,16 @@
         <v>1000</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1174,7 @@
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
@@ -1017,20 +1185,20 @@
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -1053,36 +1221,36 @@
         <v>1000</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1105,36 +1273,36 @@
         <v>1000</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A56" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1157,34 +1325,34 @@
         <v>1000</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A62" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -1193,7 +1361,7 @@
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="8">
         <v>2</v>
@@ -1218,58 +1386,58 @@
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="11">
         <v>7057527.2400000002</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="11">
         <v>7124118.9299999997</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="11">
         <v>7474829</v>
       </c>
-      <c r="E64" s="12">
+      <c r="E64" s="11">
         <v>7465423.46</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="11">
         <v>7278250.2000000002</v>
       </c>
-      <c r="G64" s="12">
+      <c r="G64" s="11">
         <v>7336149.25</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="11">
         <v>2910000.75</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="11">
         <v>869738.37</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="11">
         <v>486379.3</v>
       </c>
-      <c r="E65" s="12">
+      <c r="E65" s="11">
         <v>203258.57</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="11">
         <v>53545.05</v>
       </c>
-      <c r="G65" s="12">
+      <c r="G65" s="11">
         <v>13893.87</v>
       </c>
       <c r="H65" s="5"/>
@@ -1277,18 +1445,18 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="12">
         <v>1529252</v>
       </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12">
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11">
         <v>46757</v>
       </c>
       <c r="H66" s="7"/>
@@ -1296,25 +1464,25 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="10" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A72" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -1323,7 +1491,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="2">
         <v>1</v>
@@ -1351,10 +1519,10 @@
         <v>10</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
@@ -1369,7 +1537,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
@@ -1384,7 +1552,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -1401,13 +1569,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A72:D72"/>
@@ -1416,6 +1577,13 @@
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1425,7 +1593,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1434,7 +1602,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,9 +215,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -231,6 +228,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -538,44 +541,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.90625" style="1"/>
+    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -609,27 +612,27 @@
       <c r="L3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>30545075.399999999</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>29811997.740027301</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>30980630.497990001</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>31137398.540112801</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>16012225.6874354</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -641,65 +644,65 @@
       <c r="K4" s="1">
         <v>1000</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>30635560.517913401</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>30094194.446149699</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>31055213.250361498</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>31169257.825507801</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>16001392.5737403</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>3065244.36</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>1463248.92</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <v>2062724.5</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>2041280.3995000001</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>1937204.07</v>
       </c>
       <c r="L6" s="1">
         <v>10000000</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>1</v>
       </c>
@@ -739,29 +742,29 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>7401292</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>7365279.7479999997</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>30545075.399999999</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>30447031.229639899</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>30935064.935064901</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <v>34251061.438561402</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>34515041.776405402</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -781,29 +784,29 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>7387008.6100000003</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>7381403.0049999999</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>30635560.517913401</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <v>30651978.273827001</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>30811652.633081201</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <v>34126088.523348801</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>34653452.052534603</v>
       </c>
       <c r="K11" s="3"/>
@@ -820,29 +823,29 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>1626861.2661948199</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>1622474.0689999999</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>3065244.36</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <v>3056406.42</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="11">
         <v>3104004.67</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <v>3192249.0269999998</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>3210081.02</v>
       </c>
       <c r="K12" s="3"/>
@@ -859,7 +862,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -870,7 +873,25 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
+        <v>29655883.684660599</v>
+      </c>
+      <c r="B14" s="11">
+        <v>29456607.392607301</v>
+      </c>
+      <c r="C14" s="11">
+        <v>29233313.449140701</v>
+      </c>
+      <c r="D14" s="11">
+        <v>29137664.6609204</v>
+      </c>
+      <c r="E14" s="11">
+        <v>29233253.472191501</v>
+      </c>
+      <c r="F14" s="11">
+        <v>29070066.6240234</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -881,7 +902,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -892,43 +913,43 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14">
         <v>2</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="14">
         <v>10</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="14">
         <v>50</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="14">
         <v>100</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="14">
         <v>500</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="14">
         <v>1000</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -938,84 +959,89 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="15">
         <v>30545075.399999999</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="15">
         <v>30170030.661380101</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="15">
         <v>29975328.866937201</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="15">
         <v>29993363.038345698</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="15">
         <v>30042764.404131401</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="15">
         <v>30084216.821240999</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="12">
-        <v>29655883.684660599</v>
-      </c>
-      <c r="C20" s="12">
-        <v>29456607.392607301</v>
-      </c>
-      <c r="D20" s="12">
-        <v>29233313.449140701</v>
-      </c>
-      <c r="E20" s="12">
-        <v>29137664.6609204</v>
-      </c>
-      <c r="F20" s="12">
-        <v>29233253.472191501</v>
-      </c>
-      <c r="G20" s="12">
-        <v>29070066.6240234</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="B20" s="15">
+        <v>30060452.288225099</v>
+      </c>
+      <c r="C20" s="15">
+        <v>28474163.517641701</v>
+      </c>
+      <c r="D20" s="15">
+        <v>29134213.476686001</v>
+      </c>
+      <c r="E20" s="15">
+        <v>28472053.493951298</v>
+      </c>
+      <c r="F20" s="15">
+        <v>25737626</v>
+      </c>
+      <c r="G20" s="15">
+        <v>21581170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="15">
         <v>2673205.9300000002</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="15">
         <v>876913.8</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="15">
         <v>362475.64</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="15">
         <v>223458.038</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="15">
         <v>154271.15</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="15">
         <v>129632.158</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="D22" s="5"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B24" s="8">
         <v>2</v>
       </c>
@@ -1041,30 +1067,84 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="10">
+        <v>33302154.367371701</v>
+      </c>
+      <c r="C25" s="10">
+        <v>29279503.105590001</v>
+      </c>
+      <c r="D25" s="10">
+        <v>29755302.6683461</v>
+      </c>
+      <c r="E25" s="10">
+        <v>29368602.412080601</v>
+      </c>
+      <c r="F25" s="10">
+        <v>28875997.162340201</v>
+      </c>
+      <c r="G25" s="10">
+        <v>29934606.843319401</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="10">
+        <v>30205488.541309401</v>
+      </c>
+      <c r="C26" s="10">
+        <v>29247925.0073235</v>
+      </c>
+      <c r="D26" s="10">
+        <v>28903914.925654002</v>
+      </c>
+      <c r="E26" s="10">
+        <v>28867106.344982401</v>
+      </c>
+      <c r="F26" s="10">
+        <v>23352343.308865</v>
+      </c>
+      <c r="G26" s="10">
+        <v>20380503.5544165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="B27" s="10">
+        <v>940397.35099337704</v>
+      </c>
+      <c r="C27" s="10">
+        <v>812715.27949751203</v>
+      </c>
+      <c r="D27" s="10">
+        <v>580393.63642080105</v>
+      </c>
+      <c r="E27" s="10">
+        <v>458268.63790814299</v>
+      </c>
+      <c r="F27" s="10">
+        <v>230187.99628984401</v>
+      </c>
+      <c r="G27" s="10">
+        <v>179682.73688327501</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B30" s="8">
         <v>2</v>
       </c>
@@ -1093,45 +1173,96 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="10">
+        <v>33302154.367371701</v>
+      </c>
+      <c r="C31" s="10">
+        <v>29279503.105590001</v>
+      </c>
+      <c r="D31" s="10">
+        <v>29755302.6683461</v>
+      </c>
+      <c r="E31" s="10">
+        <v>29368602.412080601</v>
+      </c>
+      <c r="F31" s="10">
+        <v>28875997.162340201</v>
+      </c>
+      <c r="G31" s="10">
+        <v>29934606.843319401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="10">
+        <v>30205488.541309401</v>
+      </c>
+      <c r="C32" s="10">
+        <v>29247925.0073235</v>
+      </c>
+      <c r="D32" s="10">
+        <v>28903914.925654002</v>
+      </c>
+      <c r="E32" s="10">
+        <v>28867106.344982401</v>
+      </c>
+      <c r="F32" s="10">
+        <v>23352343.308865</v>
+      </c>
+      <c r="G32" s="10">
+        <v>20380503.5544165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
+      <c r="B33" s="10">
+        <v>940397.35099337704</v>
+      </c>
+      <c r="C33" s="10">
+        <v>812715.27949751203</v>
+      </c>
+      <c r="D33" s="10">
+        <v>580393.63642080105</v>
+      </c>
+      <c r="E33" s="10">
+        <v>458268.63790814299</v>
+      </c>
+      <c r="F33" s="10">
+        <v>230187.99628984401</v>
+      </c>
+      <c r="G33" s="10">
+        <v>179682.73688327501</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B39" s="1">
         <v>2</v>
       </c>
@@ -1145,12 +1276,9 @@
         <v>100</v>
       </c>
       <c r="F39" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G39" s="1">
-        <v>500</v>
-      </c>
-      <c r="H39" s="1">
         <v>1000</v>
       </c>
       <c r="J39" s="1" t="s">
@@ -1163,42 +1291,84 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="15">
         <v>30545075.399999999</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C40" s="15">
+        <v>30170030.661380101</v>
+      </c>
+      <c r="D40" s="15">
+        <v>29975328.866937201</v>
+      </c>
+      <c r="E40" s="15">
+        <v>29993363.038345698</v>
+      </c>
+      <c r="F40" s="15">
+        <v>30042764.404131401</v>
+      </c>
+      <c r="G40" s="15">
+        <v>30084216.821240999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="5">
-        <v>29117997.387228101</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B41" s="15">
+        <v>30060452.288225099</v>
+      </c>
+      <c r="C41" s="15">
+        <v>28474163.517641701</v>
+      </c>
+      <c r="D41" s="15">
+        <v>29134213.476686001</v>
+      </c>
+      <c r="E41" s="15">
+        <v>28472053.493951298</v>
+      </c>
+      <c r="F41" s="15">
+        <v>25737626</v>
+      </c>
+      <c r="G41" s="15">
+        <v>21581170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
+      <c r="B42" s="15">
+        <v>2673205.9300000002</v>
+      </c>
+      <c r="C42" s="15">
+        <v>876913.8</v>
+      </c>
+      <c r="D42" s="15">
+        <v>362475.64</v>
+      </c>
+      <c r="E42" s="15">
+        <v>223458.038</v>
+      </c>
+      <c r="F42" s="15">
+        <v>154271.15</v>
+      </c>
+      <c r="G42" s="15">
+        <v>129632.158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A44" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -1212,12 +1382,9 @@
         <v>100</v>
       </c>
       <c r="F45" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G45" s="1">
-        <v>500</v>
-      </c>
-      <c r="H45" s="1">
         <v>1000</v>
       </c>
       <c r="J45" s="1" t="s">
@@ -1227,30 +1394,30 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="13" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1279,30 +1446,30 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="13" t="s">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A56" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1331,28 +1498,28 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="13" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A62" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -1361,7 +1528,7 @@
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="7"/>
       <c r="B63" s="8">
         <v>2</v>
@@ -1381,9 +1548,7 @@
       <c r="G63" s="8">
         <v>1000</v>
       </c>
-      <c r="H63" s="7">
-        <v>1000</v>
-      </c>
+      <c r="H63" s="7"/>
       <c r="I63" s="7"/>
       <c r="J63" s="7" t="s">
         <v>20</v>
@@ -1392,52 +1557,52 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="10">
         <v>7057527.2400000002</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="10">
         <v>7124118.9299999997</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="10">
         <v>7474829</v>
       </c>
-      <c r="E64" s="11">
+      <c r="E64" s="10">
         <v>7465423.46</v>
       </c>
-      <c r="F64" s="11">
+      <c r="F64" s="10">
         <v>7278250.2000000002</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G64" s="10">
         <v>7336149.25</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="10">
         <v>2910000.75</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>869738.37</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <v>486379.3</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="10">
         <v>203258.57</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="10">
         <v>53545.05</v>
       </c>
-      <c r="G65" s="11">
+      <c r="G65" s="10">
         <v>13893.87</v>
       </c>
       <c r="H65" s="5"/>
@@ -1445,18 +1610,18 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="11">
         <v>1529252</v>
       </c>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11">
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10">
         <v>46757</v>
       </c>
       <c r="H66" s="7"/>
@@ -1464,25 +1629,25 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="13" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="14" t="s">
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -1491,7 +1656,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2">
         <v>1</v>
@@ -1522,7 +1687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1702,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
@@ -1552,7 +1717,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -1569,6 +1734,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A72:D72"/>
@@ -1577,13 +1749,6 @@
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1593,7 +1758,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1602,7 +1767,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -224,16 +224,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -541,44 +544,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="1"/>
-    <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.90625" style="1"/>
-    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -616,7 +619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
@@ -648,7 +651,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
@@ -671,7 +674,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -694,15 +697,15 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1</v>
       </c>
@@ -742,7 +745,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
@@ -784,7 +787,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>2</v>
       </c>
@@ -823,7 +826,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>1</v>
       </c>
@@ -862,7 +865,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -873,7 +876,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>29655883.684660599</v>
       </c>
@@ -902,7 +905,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -913,43 +916,43 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12">
         <v>2</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <v>10</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <v>50</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>100</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="12">
         <v>500</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="12">
         <v>1000</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -959,89 +962,89 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="11">
         <v>30545075.399999999</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="11">
         <v>30170030.661380101</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="11">
         <v>29975328.866937201</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="11">
         <v>29993363.038345698</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="11">
         <v>30042764.404131401</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="11">
         <v>30084216.821240999</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="15">
-        <v>30060452.288225099</v>
-      </c>
-      <c r="C20" s="15">
-        <v>28474163.517641701</v>
-      </c>
-      <c r="D20" s="15">
-        <v>29134213.476686001</v>
-      </c>
-      <c r="E20" s="15">
-        <v>28472053.493951298</v>
-      </c>
-      <c r="F20" s="15">
-        <v>25737626</v>
-      </c>
-      <c r="G20" s="15">
-        <v>21581170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="14" t="s">
+      <c r="B20" s="16">
+        <v>30479626.5187326</v>
+      </c>
+      <c r="C20" s="16">
+        <v>31324675.614588201</v>
+      </c>
+      <c r="D20" s="16">
+        <v>29964381.986728299</v>
+      </c>
+      <c r="E20" s="16">
+        <v>29349968.4672869</v>
+      </c>
+      <c r="F20" s="16">
+        <v>28848375.088598501</v>
+      </c>
+      <c r="G20" s="16">
+        <v>29608626.273055799</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="11">
         <v>2673205.9300000002</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="11">
         <v>876913.8</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="11">
         <v>362475.64</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="11">
         <v>223458.038</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="11">
         <v>154271.15</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="11">
         <v>129632.158</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D22" s="5"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <v>2</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,30 +1093,30 @@
         <v>29934606.843319401</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="10">
-        <v>30205488.541309401</v>
-      </c>
-      <c r="C26" s="10">
-        <v>29247925.0073235</v>
-      </c>
-      <c r="D26" s="10">
-        <v>28903914.925654002</v>
-      </c>
-      <c r="E26" s="10">
-        <v>28867106.344982401</v>
-      </c>
-      <c r="F26" s="10">
-        <v>23352343.308865</v>
-      </c>
-      <c r="G26" s="10">
-        <v>20380503.5544165</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B26" s="5">
+        <v>28434708.148993801</v>
+      </c>
+      <c r="C26" s="5">
+        <v>30425937.191300299</v>
+      </c>
+      <c r="D26" s="5">
+        <v>27880281.729443699</v>
+      </c>
+      <c r="E26" s="5">
+        <v>28941059.2700078</v>
+      </c>
+      <c r="F26" s="5">
+        <v>25502731.9049665</v>
+      </c>
+      <c r="G26" s="5">
+        <v>18799601.524698202</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
@@ -1136,15 +1139,23 @@
         <v>179682.73688327501</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="12" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <v>2</v>
       </c>
@@ -1173,7 +1184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1207,7 @@
         <v>29934606.843319401</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
@@ -1219,7 +1230,7 @@
         <v>20380503.5544165</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -1242,27 +1253,35 @@
         <v>179682.73688327501</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37" s="12" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="12" t="s">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
         <v>2</v>
       </c>
@@ -1291,84 +1310,84 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="15">
-        <v>30545075.399999999</v>
-      </c>
-      <c r="C40" s="15">
-        <v>30170030.661380101</v>
-      </c>
-      <c r="D40" s="15">
-        <v>29975328.866937201</v>
-      </c>
-      <c r="E40" s="15">
-        <v>29993363.038345698</v>
-      </c>
-      <c r="F40" s="15">
+      <c r="B40" s="16">
+        <v>30307142.010531802</v>
+      </c>
+      <c r="C40" s="16">
+        <v>29679774.0075051</v>
+      </c>
+      <c r="D40" s="16">
+        <v>29672226.932731099</v>
+      </c>
+      <c r="E40" s="16">
+        <v>29068418.975981999</v>
+      </c>
+      <c r="F40" s="13">
         <v>30042764.404131401</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="13">
         <v>30084216.821240999</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="13">
         <v>30060452.288225099</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="13">
         <v>28474163.517641701</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="13">
         <v>29134213.476686001</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="13">
         <v>28472053.493951298</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="13">
         <v>25737626</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="13">
         <v>21581170</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="13">
         <v>2673205.9300000002</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="13">
         <v>876913.8</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="13">
         <v>362475.64</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="13">
         <v>223458.038</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="13">
         <v>154271.15</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="13">
         <v>129632.158</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="12" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -1394,30 +1413,30 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="12" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1446,30 +1465,30 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A56" s="12" t="s">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1498,28 +1517,28 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A62" s="12" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -1528,7 +1547,7 @@
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="8">
         <v>2</v>
@@ -1557,7 +1576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>0</v>
       </c>
@@ -1583,7 +1602,7 @@
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>2</v>
       </c>
@@ -1610,7 +1629,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>1</v>
       </c>
@@ -1629,25 +1648,25 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="12" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A72" s="13" t="s">
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -1656,7 +1675,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="2">
         <v>1</v>
@@ -1687,7 +1706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
@@ -1702,7 +1721,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
@@ -1717,7 +1736,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -1734,13 +1753,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A72:D72"/>
@@ -1749,6 +1761,13 @@
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1758,7 +1777,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1767,7 +1786,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,12 +87,6 @@
     <t>max + median</t>
   </si>
   <si>
-    <t>sum + max</t>
-  </si>
-  <si>
-    <t>sum + median</t>
-  </si>
-  <si>
     <t>tumbling + countbased</t>
   </si>
   <si>
@@ -127,6 +121,12 @@
   </si>
   <si>
     <t>tumbling + punctuation</t>
+  </si>
+  <si>
+    <t>Average + max</t>
+  </si>
+  <si>
+    <t>Average + median</t>
   </si>
 </sst>
 </file>
@@ -230,13 +230,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -544,44 +544,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.90625" style="1"/>
+    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -619,7 +619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
@@ -639,7 +639,7 @@
         <v>16012225.6874354</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J4" s="1">
         <v>1000</v>
@@ -648,10 +648,10 @@
         <v>1000</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
@@ -671,10 +671,10 @@
         <v>16001392.5737403</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -697,15 +697,15 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>1</v>
       </c>
@@ -722,7 +722,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>13</v>
@@ -736,7 +736,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -745,7 +745,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>0</v>
       </c>
@@ -771,7 +771,7 @@
         <v>34515041.776405402</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="4">
@@ -787,7 +787,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>2</v>
       </c>
@@ -826,7 +826,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>1</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -876,7 +876,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>29655883.684660599</v>
       </c>
@@ -905,7 +905,7 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -916,26 +916,26 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="12">
         <v>2</v>
@@ -959,10 +959,10 @@
         <v>10</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>0</v>
       </c>
@@ -985,30 +985,30 @@
         <v>30084216.821240999</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="14">
         <v>30479626.5187326</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="14">
         <v>31324675.614588201</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="14">
         <v>29964381.986728299</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="14">
         <v>29349968.4672869</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="14">
         <v>28848375.088598501</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="14">
         <v>29608626.273055799</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>1</v>
       </c>
@@ -1031,20 +1031,20 @@
         <v>129632.158</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D22" s="5"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B24" s="8">
         <v>2</v>
       </c>
@@ -1067,10 +1067,10 @@
         <v>10</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>29934606.843319401</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>18799601.524698202</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>179682.73688327501</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="10"/>
@@ -1147,15 +1147,15 @@
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B30" s="8">
         <v>2</v>
       </c>
@@ -1178,13 +1178,13 @@
         <v>10</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>29934606.843319401</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>20380503.5544165</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>1</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>179682.73688327501</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -1261,27 +1261,27 @@
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B39" s="1">
         <v>2</v>
       </c>
@@ -1310,20 +1310,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="14">
         <v>30307142.010531802</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="14">
         <v>29679774.0075051</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="14">
         <v>29672226.932731099</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="14">
         <v>29068418.975981999</v>
       </c>
       <c r="F40" s="13">
@@ -1333,7 +1333,7 @@
         <v>30084216.821240999</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>21581170</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
@@ -1379,15 +1379,15 @@
         <v>129632.158</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A44" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B45" s="1">
         <v>1</v>
       </c>
@@ -1413,30 +1413,30 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B51" s="1">
         <v>1</v>
       </c>
@@ -1462,33 +1462,33 @@
         <v>20</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="14" t="s">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A56" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B57" s="1">
         <v>1</v>
       </c>
@@ -1514,31 +1514,31 @@
         <v>20</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="14" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A62" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -1547,7 +1547,7 @@
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="7"/>
       <c r="B63" s="8">
         <v>2</v>
@@ -1573,10 +1573,10 @@
         <v>20</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>0</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>2</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>1</v>
       </c>
@@ -1648,25 +1648,25 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="15"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -1675,7 +1675,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2">
         <v>1</v>
@@ -1703,10 +1703,10 @@
         <v>10</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>2</v>
       </c>
@@ -1736,7 +1736,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -1777,7 +1777,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1786,7 +1786,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -264,16 +264,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -581,44 +581,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S107"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="9.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.90625" style="1"/>
+    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -656,7 +656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
@@ -688,7 +688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
@@ -711,7 +711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>35</v>
       </c>
@@ -730,9 +730,9 @@
       <c r="F6" s="10">
         <v>15967132.949999999</v>
       </c>
-      <c r="G6" s="17"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="G6" s="15"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>1</v>
       </c>
@@ -755,15 +755,15 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>1</v>
       </c>
@@ -803,7 +803,7 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>0</v>
       </c>
@@ -845,7 +845,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>2</v>
       </c>
@@ -884,7 +884,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>35</v>
       </c>
@@ -919,7 +919,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>1</v>
       </c>
@@ -958,7 +958,7 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -969,7 +969,7 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -986,7 +986,7 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -997,26 +997,26 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
       <c r="B20" s="11">
         <v>2</v>
@@ -1043,8 +1043,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A21" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="10">
@@ -1066,8 +1066,8 @@
         <v>31029385.726073898</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B22" s="10">
@@ -1089,7 +1089,7 @@
         <v>28742027.523211598</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>35</v>
       </c>
@@ -1112,8 +1112,8 @@
         <v>27494.240000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A24" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B24" s="10">
@@ -1135,20 +1135,20 @@
         <v>46494.372000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D25" s="4"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="7"/>
       <c r="B27" s="7">
         <v>2</v>
@@ -1175,7 +1175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>0</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>30395262.192525599</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>2</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>27521084.598988298</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>35</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>23324.5</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>1</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>96959.26</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="9"/>
@@ -1275,15 +1275,15 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
       <c r="B34" s="7">
         <v>2</v>
@@ -1313,12 +1313,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B35" s="10">
-        <v>33302154.367371701</v>
+        <v>31193128.444963999</v>
       </c>
       <c r="C35" s="10">
         <v>29279503.105590001</v>
@@ -1336,7 +1336,7 @@
         <v>29934606.843319401</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>2</v>
       </c>
@@ -1353,13 +1353,13 @@
         <v>28867106.344982401</v>
       </c>
       <c r="F36" s="10">
-        <v>23352343.308865</v>
+        <v>27244764.800213799</v>
       </c>
       <c r="G36" s="10">
-        <v>20380503.5544165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.3">
+        <v>27535714.0471243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>35</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>25482.79</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>1</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>117525.4</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -1413,27 +1413,27 @@
       <c r="F39" s="9"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="14" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="14" t="s">
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="7"/>
       <c r="B44" s="7">
         <v>2</v>
@@ -1463,7 +1463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>0</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>31680790.497986998</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>2</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>16988246.2212837</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>35</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>30287.43</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>1</v>
       </c>
@@ -1555,15 +1555,15 @@
         <v>48988.256880000001</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
       <c r="B51" s="7">
         <v>2</v>
@@ -1590,7 +1590,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>0</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>7162900.2000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>2</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>419277.30771089502</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>35</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>7304.3</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>1</v>
       </c>
@@ -1682,15 +1682,15 @@
         <v>40801</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A57" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="7"/>
       <c r="B58" s="7">
         <v>2</v>
@@ -1717,7 +1717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>0</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>28595004.6272012</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>2</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>16713713.436127</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>35</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>30023.488000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>1</v>
       </c>
@@ -1809,15 +1809,15 @@
         <v>49702.896000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="14" t="s">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A64" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="7"/>
       <c r="B65" s="7">
         <v>2</v>
@@ -1844,7 +1844,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>0</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>7153667.2599999998</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>2</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>417719.89997231198</v>
       </c>
     </row>
-    <row r="68" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>35</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>8889.5324341247997</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>1</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>41439.678</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B70" s="13"/>
       <c r="C70" s="13"/>
       <c r="D70" s="13"/>
@@ -1944,13 +1944,13 @@
       <c r="F70" s="13"/>
       <c r="G70" s="13"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -1959,7 +1959,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="7"/>
       <c r="B72" s="7">
         <v>2</v>
@@ -1988,7 +1988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>0</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>2</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
     </row>
-    <row r="75" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>35</v>
       </c>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>1</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B77" s="13"/>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -2100,7 +2100,7 @@
       <c r="F77" s="13"/>
       <c r="G77" s="13"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="13" t="s">
         <v>38</v>
       </c>
@@ -2131,7 +2131,7 @@
       <c r="J79" s="13"/>
       <c r="K79" s="13"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="13" t="s">
         <v>40</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="13" t="s">
         <v>38</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
         <v>38</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>41</v>
       </c>
@@ -2244,27 +2244,27 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="14" t="s">
+    <row r="86" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A92" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B92" s="14"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
       <c r="I92" s="13"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" s="16" t="s">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A93" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B93" s="16"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="16"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
@@ -2277,7 +2277,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="7"/>
       <c r="B94" s="7">
         <v>2</v>
@@ -2302,7 +2302,7 @@
       <c r="J94" s="13"/>
       <c r="K94" s="13"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>0</v>
       </c>
@@ -2317,7 +2317,7 @@
       <c r="J95" s="13"/>
       <c r="K95" s="13"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>2</v>
       </c>
@@ -2332,7 +2332,7 @@
       <c r="J96" s="13"/>
       <c r="K96" s="13"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>35</v>
       </c>
@@ -2347,7 +2347,7 @@
       <c r="J97" s="13"/>
       <c r="K97" s="13"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>1</v>
       </c>
@@ -2362,30 +2362,30 @@
       <c r="J98" s="13"/>
       <c r="K98" s="13"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="I99" s="13"/>
       <c r="J99" s="13"/>
       <c r="K99" s="13"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" s="14" t="s">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A101" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B101" s="14"/>
-      <c r="C101" s="14"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="14"/>
-      <c r="F101" s="14"/>
-      <c r="G101" s="14"/>
-      <c r="H101" s="14"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A102" s="16" t="s">
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A102" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B102" s="16"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="16"/>
+      <c r="B102" s="17"/>
+      <c r="C102" s="17"/>
+      <c r="D102" s="17"/>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -2397,7 +2397,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="7"/>
       <c r="B103" s="7">
         <v>2</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H103" s="13"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
         <v>0</v>
       </c>
@@ -2431,7 +2431,7 @@
       <c r="G104" s="7"/>
       <c r="H104" s="13"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>2</v>
       </c>
@@ -2443,7 +2443,7 @@
       <c r="G105" s="7"/>
       <c r="H105" s="13"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>35</v>
       </c>
@@ -2455,7 +2455,7 @@
       <c r="G106" s="7"/>
       <c r="H106" s="13"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>1</v>
       </c>
@@ -2469,23 +2469,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A92:H92"/>
     <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A93:D93"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A93:D93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2495,7 +2495,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2504,7 +2504,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -2469,6 +2469,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A93:D93"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A9:D9"/>
@@ -2480,12 +2486,6 @@
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A93:D93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="52">
   <si>
     <t>Desis</t>
   </si>
@@ -84,9 +84,6 @@
     <t>average + sum</t>
   </si>
   <si>
-    <t>tumbling + countbased</t>
-  </si>
-  <si>
     <t>Mix Window Measure</t>
   </si>
   <si>
@@ -153,7 +150,28 @@
     <t>sort+</t>
   </si>
   <si>
-    <t>countbased + countbased</t>
+    <t>Slices</t>
+  </si>
+  <si>
+    <t>tumbling + tumbling</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>5m</t>
+  </si>
+  <si>
+    <t>tumbling + Punctuation</t>
+  </si>
+  <si>
+    <t>average sum</t>
+  </si>
+  <si>
+    <t>calculations</t>
+  </si>
+  <si>
+    <t>1 M</t>
   </si>
 </sst>
 </file>
@@ -223,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -268,6 +286,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -580,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S107"/>
+  <dimension ref="A1:S130"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1"/>
@@ -591,7 +615,7 @@
     <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.90625" style="1"/>
+    <col min="9" max="9" width="23" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="22.6328125" style="1" customWidth="1"/>
     <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
@@ -600,23 +624,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
@@ -676,7 +700,7 @@
         <v>16012225.6874354</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J4" s="1">
         <v>1000</v>
@@ -685,7 +709,7 @@
         <v>1000</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -708,12 +732,12 @@
         <v>16001392.5737403</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="10">
         <v>31256010.267402299</v>
@@ -756,12 +780,12 @@
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
@@ -780,7 +804,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>13</v>
@@ -794,7 +818,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -829,7 +853,7 @@
         <v>36166162.255541898</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3">
@@ -886,7 +910,7 @@
     </row>
     <row r="13" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="10">
         <v>7231345.29</v>
@@ -998,23 +1022,23 @@
       <c r="S17" s="2"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
@@ -1040,7 +1064,7 @@
         <v>10</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
@@ -1091,7 +1115,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="10">
         <v>16294481.4382941</v>
@@ -1141,12 +1165,12 @@
       <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="7"/>
@@ -1172,7 +1196,7 @@
         <v>10</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
@@ -1223,7 +1247,7 @@
     </row>
     <row r="30" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="10">
         <v>16416701.864478299</v>
@@ -1276,12 +1300,12 @@
       <c r="G32" s="9"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
@@ -1307,10 +1331,10 @@
         <v>10</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
@@ -1361,7 +1385,7 @@
     </row>
     <row r="37" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="10">
         <v>16277423.3504701</v>
@@ -1414,24 +1438,24 @@
       <c r="G39" s="9"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="7"/>
@@ -1511,7 +1535,7 @@
     </row>
     <row r="47" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B47" s="12">
         <v>16882342.524749301</v>
@@ -1556,12 +1580,12 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
@@ -1587,7 +1611,7 @@
         <v>20</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -1638,7 +1662,7 @@
     </row>
     <row r="54" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B54" s="10">
         <v>5365348.7582951402</v>
@@ -1683,12 +1707,12 @@
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="7"/>
@@ -1714,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -1765,7 +1789,7 @@
     </row>
     <row r="61" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B61" s="10">
         <v>16705429.4228661</v>
@@ -1810,12 +1834,12 @@
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="7"/>
@@ -1841,7 +1865,7 @@
         <v>20</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -1892,7 +1916,7 @@
     </row>
     <row r="68" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B68" s="10">
         <v>5237469.5028360896</v>
@@ -1945,12 +1969,12 @@
       <c r="G70" s="13"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -1985,7 +2009,7 @@
         <v>20</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -2043,7 +2067,7 @@
     </row>
     <row r="75" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B75" s="10">
         <v>5360754.2921310998</v>
@@ -2102,7 +2126,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B79" s="13">
         <v>0.84277000000000002</v>
@@ -2123,17 +2147,17 @@
         <v>0.84260000000000002</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J79" s="13"/>
       <c r="K79" s="13"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B80" s="13">
         <v>0.82383250683169196</v>
@@ -2154,15 +2178,15 @@
         <v>1.4679206336003E-3</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B81" s="13">
         <v>0.89829001804841502</v>
@@ -2183,15 +2207,15 @@
         <v>6.9468576422784797E-2</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B82" s="13">
         <v>0.40171929990427002</v>
@@ -2212,15 +2236,15 @@
         <v>1.9348417088597E-3</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B83" s="13">
         <v>2910000.75</v>
@@ -2241,64 +2265,63 @@
         <v>13893.87</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="92" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A92" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
-      <c r="H92" s="16"/>
+      <c r="A92" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
+      <c r="H92" s="18"/>
       <c r="I92" s="13"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A93" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
+      <c r="A93" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="19"/>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
       <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="K93" s="13" t="s">
-        <v>22</v>
-      </c>
+      <c r="I93" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J93" s="13"/>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="7"/>
-      <c r="B94" s="7">
+      <c r="B94" s="10">
         <v>2</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="10">
         <v>10</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="10">
         <v>50</v>
       </c>
-      <c r="E94" s="7">
+      <c r="E94" s="10">
         <v>100</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F94" s="10">
         <v>500</v>
       </c>
-      <c r="G94" s="7">
+      <c r="G94" s="10">
         <v>1000</v>
       </c>
       <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
+      <c r="I94" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="J94" s="13"/>
       <c r="K94" s="13"/>
     </row>
@@ -2306,14 +2329,28 @@
       <c r="A95" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
+      <c r="B95" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C95" s="10">
+        <v>61</v>
+      </c>
+      <c r="D95" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="E95" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="F95" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="G95" s="10">
+        <v>60.8</v>
+      </c>
       <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
+      <c r="I95" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="J95" s="13"/>
       <c r="K95" s="13"/>
     </row>
@@ -2321,56 +2358,90 @@
       <c r="A96" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
+      <c r="B96" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C96" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="D96" s="10">
+        <v>61</v>
+      </c>
+      <c r="E96" s="10">
+        <v>61</v>
+      </c>
+      <c r="F96" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="G96" s="10">
+        <v>60.8</v>
+      </c>
       <c r="H96" s="13"/>
       <c r="I96" s="13"/>
       <c r="J96" s="13"/>
       <c r="K96" s="13"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
+        <v>34</v>
+      </c>
+      <c r="B97" s="10">
+        <v>90.8</v>
+      </c>
+      <c r="C97" s="10">
+        <v>177.8</v>
+      </c>
+      <c r="D97" s="10">
+        <v>883.4</v>
+      </c>
+      <c r="E97" s="10">
+        <v>1766.4</v>
+      </c>
+      <c r="F97" s="10">
+        <v>8870.4</v>
+      </c>
+      <c r="G97" s="10">
+        <v>17755.599999999999</v>
+      </c>
       <c r="H97" s="13"/>
       <c r="I97" s="13"/>
       <c r="J97" s="13"/>
       <c r="K97" s="13"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
+      <c r="B98" s="10">
+        <v>90.8</v>
+      </c>
+      <c r="C98" s="10">
+        <v>179.4</v>
+      </c>
+      <c r="D98" s="10">
+        <v>887.8</v>
+      </c>
+      <c r="E98" s="10">
+        <v>1784</v>
+      </c>
+      <c r="F98" s="10">
+        <v>9313.7999999999993</v>
+      </c>
+      <c r="G98" s="10">
+        <v>17933</v>
+      </c>
       <c r="H98" s="13"/>
       <c r="I98" s="13"/>
       <c r="J98" s="13"/>
       <c r="K98" s="13"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="I99" s="13"/>
       <c r="J99" s="13"/>
       <c r="K99" s="13"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A101" s="16" t="s">
-        <v>17</v>
-      </c>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A101" s="16"/>
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
       <c r="D101" s="16"/>
@@ -2378,103 +2449,606 @@
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
       <c r="H101" s="16"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A102" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B102" s="17"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="17"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="13"/>
-      <c r="J102" s="13" t="s">
+      <c r="I101" s="16"/>
+      <c r="J101" s="16"/>
+      <c r="K101" s="16"/>
+      <c r="L101" s="16"/>
+      <c r="M101" s="16"/>
+      <c r="N101" s="16"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A102" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B102" s="18"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18"/>
+      <c r="G102" s="18"/>
+      <c r="H102" s="18"/>
+      <c r="I102" s="16"/>
+      <c r="J102" s="16"/>
+      <c r="K102" s="16"/>
+      <c r="L102" s="16"/>
+      <c r="M102" s="16"/>
+      <c r="N102" s="16"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A103" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="19"/>
+      <c r="C103" s="19"/>
+      <c r="D103" s="19"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17"/>
+      <c r="G103" s="17"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J103" s="16"/>
+      <c r="K103" s="16"/>
+      <c r="L103" s="16"/>
+      <c r="M103" s="16"/>
+      <c r="N103" s="16"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A104" s="17"/>
+      <c r="B104" s="17">
+        <v>2</v>
+      </c>
+      <c r="C104" s="17">
         <v>10</v>
       </c>
-      <c r="K102" s="13" t="s">
+      <c r="D104" s="17">
+        <v>50</v>
+      </c>
+      <c r="E104" s="17">
+        <v>100</v>
+      </c>
+      <c r="F104" s="17">
+        <v>500</v>
+      </c>
+      <c r="G104" s="17">
+        <v>1000</v>
+      </c>
+      <c r="H104" s="16"/>
+      <c r="I104" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J104" s="16"/>
+      <c r="K104" s="16"/>
+      <c r="L104" s="16"/>
+      <c r="M104" s="16"/>
+      <c r="N104" s="16"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A105" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="10">
+        <v>111.6</v>
+      </c>
+      <c r="C105" s="10">
+        <v>255.4</v>
+      </c>
+      <c r="D105" s="10">
+        <v>384.6</v>
+      </c>
+      <c r="E105" s="10">
+        <v>381.2</v>
+      </c>
+      <c r="F105" s="10">
+        <v>376</v>
+      </c>
+      <c r="G105" s="10">
+        <v>391.6</v>
+      </c>
+      <c r="H105" s="16"/>
+      <c r="I105" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J105" s="16"/>
+      <c r="K105" s="16"/>
+      <c r="L105" s="16"/>
+      <c r="M105" s="16"/>
+      <c r="N105" s="16"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A106" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" s="10">
+        <v>111.8</v>
+      </c>
+      <c r="C106" s="10">
+        <v>252.8</v>
+      </c>
+      <c r="D106" s="10">
+        <v>382.6</v>
+      </c>
+      <c r="E106" s="10">
+        <v>403.4</v>
+      </c>
+      <c r="F106" s="10">
+        <v>386.8</v>
+      </c>
+      <c r="G106" s="10">
+        <v>382.8</v>
+      </c>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="16"/>
+      <c r="K106" s="16"/>
+      <c r="L106" s="16"/>
+      <c r="M106" s="16"/>
+      <c r="N106" s="16"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A107" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B107" s="10">
+        <v>124</v>
+      </c>
+      <c r="C107" s="10">
+        <v>440</v>
+      </c>
+      <c r="D107" s="10">
+        <v>2003</v>
+      </c>
+      <c r="E107" s="10">
+        <v>3908.2</v>
+      </c>
+      <c r="F107" s="10">
+        <v>19415.8</v>
+      </c>
+      <c r="G107" s="10">
+        <v>39632.800000000003</v>
+      </c>
+      <c r="H107" s="16"/>
+      <c r="I107" s="16"/>
+      <c r="J107" s="16"/>
+      <c r="K107" s="16"/>
+      <c r="L107" s="16"/>
+      <c r="M107" s="16"/>
+      <c r="N107" s="16"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A108" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B108" s="10">
+        <v>124</v>
+      </c>
+      <c r="C108" s="10">
+        <v>444.4</v>
+      </c>
+      <c r="D108" s="10">
+        <v>2043</v>
+      </c>
+      <c r="E108" s="10">
+        <v>3986.2</v>
+      </c>
+      <c r="F108" s="10">
+        <v>19221.599999999999</v>
+      </c>
+      <c r="G108" s="10">
+        <v>40029</v>
+      </c>
+      <c r="H108" s="16"/>
+      <c r="I108" s="16"/>
+      <c r="J108" s="16"/>
+      <c r="K108" s="16"/>
+      <c r="L108" s="16"/>
+      <c r="M108" s="16"/>
+      <c r="N108" s="16"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A109" s="16"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="16"/>
+      <c r="H109" s="16"/>
+      <c r="I109" s="16"/>
+      <c r="J109" s="16"/>
+      <c r="K109" s="16"/>
+      <c r="L109" s="16"/>
+      <c r="M109" s="16"/>
+      <c r="N109" s="16"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A110" s="16"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="16"/>
+      <c r="H110" s="16"/>
+      <c r="J110" s="16"/>
+      <c r="K110" s="16"/>
+      <c r="L110" s="16"/>
+      <c r="M110" s="16"/>
+      <c r="N110" s="16"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B111" s="16"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="16"/>
+      <c r="J111" s="16"/>
+      <c r="K111" s="16"/>
+      <c r="L111" s="16"/>
+      <c r="M111" s="16"/>
+      <c r="N111" s="16"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A112" s="16"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16"/>
+      <c r="I112" s="16"/>
+      <c r="J112" s="16"/>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
+      <c r="M112" s="16"/>
+      <c r="N112" s="16"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16"/>
+      <c r="I113" s="16"/>
+      <c r="J113" s="16"/>
+      <c r="K113" s="16"/>
+      <c r="L113" s="16"/>
+      <c r="M113" s="16"/>
+      <c r="N113" s="16"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A114" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B114" s="18"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="16"/>
+      <c r="J114" s="16"/>
+      <c r="K114" s="16"/>
+      <c r="L114" s="16"/>
+      <c r="M114" s="16"/>
+      <c r="N114" s="16"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A115" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115" s="19"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="19"/>
+      <c r="E115" s="17"/>
+      <c r="F115" s="17"/>
+      <c r="G115" s="17"/>
+      <c r="H115" s="16"/>
+      <c r="I115" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A116" s="17"/>
+      <c r="B116" s="10">
         <v>2</v>
       </c>
-      <c r="C103" s="7">
+      <c r="C116" s="10">
         <v>10</v>
       </c>
-      <c r="D103" s="7">
+      <c r="D116" s="10">
         <v>50</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E116" s="10">
         <v>100</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F116" s="10">
         <v>500</v>
       </c>
-      <c r="G103" s="7">
+      <c r="G116" s="10">
         <v>1000</v>
       </c>
-      <c r="H103" s="13"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A104" s="7" t="s">
+      <c r="H116" s="16"/>
+      <c r="I116" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A117" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="13"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A105" s="7" t="s">
+      <c r="B117" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="C117" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="D117" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="E117" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="F117" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="G117" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="H117" s="16"/>
+      <c r="I117" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A118" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B105" s="7"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="13"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A106" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="13"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A107" s="7" t="s">
+      <c r="B118" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="C118" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="D118" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="E118" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="F118" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="G118" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="H118" s="16"/>
+      <c r="I118" s="16"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A119" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="C119" s="10">
+        <v>15000000</v>
+      </c>
+      <c r="D119" s="10">
+        <v>75000000</v>
+      </c>
+      <c r="E119" s="10">
+        <v>150000000</v>
+      </c>
+      <c r="F119" s="10">
+        <v>750000000</v>
+      </c>
+      <c r="G119" s="10">
+        <v>1500000000</v>
+      </c>
+      <c r="H119" s="16"/>
+      <c r="I119" s="16"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A120" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B107" s="7"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="13"/>
+      <c r="B120" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="C120" s="10">
+        <v>15000000</v>
+      </c>
+      <c r="D120" s="10">
+        <v>75000000</v>
+      </c>
+      <c r="E120" s="10">
+        <v>150000000</v>
+      </c>
+      <c r="F120" s="10">
+        <v>750000000</v>
+      </c>
+      <c r="G120" s="10">
+        <v>1500000000</v>
+      </c>
+      <c r="H120" s="16"/>
+      <c r="I120" s="16"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A121" s="16"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A124" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B124" s="18"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="18"/>
+      <c r="G124" s="18"/>
+      <c r="H124" s="18"/>
+      <c r="I124" s="16"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A125" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" s="19"/>
+      <c r="C125" s="19"/>
+      <c r="D125" s="19"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="17"/>
+      <c r="G125" s="17"/>
+      <c r="H125" s="16"/>
+      <c r="I125" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A126" s="17"/>
+      <c r="B126" s="10">
+        <v>2</v>
+      </c>
+      <c r="C126" s="10">
+        <v>10</v>
+      </c>
+      <c r="D126" s="10">
+        <v>50</v>
+      </c>
+      <c r="E126" s="10">
+        <v>100</v>
+      </c>
+      <c r="F126" s="10">
+        <v>500</v>
+      </c>
+      <c r="G126" s="10">
+        <v>1000</v>
+      </c>
+      <c r="H126" s="16"/>
+      <c r="I126" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A127" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="C127" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="D127" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="E127" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="F127" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G127" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="H127" s="16"/>
+      <c r="I127" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A128" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B128" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="C128" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="D128" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="E128" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="F128" s="10">
+        <v>500000000</v>
+      </c>
+      <c r="G128" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="H128" s="16"/>
+      <c r="I128" s="16"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A129" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="C129" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="D129" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="E129" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="F129" s="10">
+        <v>500000000</v>
+      </c>
+      <c r="G129" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="H129" s="16"/>
+      <c r="I129" s="16"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A130" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B130" s="10">
+        <v>2000000</v>
+      </c>
+      <c r="C130" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="D130" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="E130" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="F130" s="10">
+        <v>500000000</v>
+      </c>
+      <c r="G130" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="H130" s="16"/>
+      <c r="I130" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A93:D93"/>
+  <mergeCells count="21">
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A114:H114"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A124:H124"/>
+    <mergeCell ref="A125:D125"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A9:D9"/>
@@ -2486,6 +3060,11 @@
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A102:H102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2494,9 +3073,359 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17">
+        <v>2</v>
+      </c>
+      <c r="C3" s="17">
+        <v>10</v>
+      </c>
+      <c r="D3" s="17">
+        <v>50</v>
+      </c>
+      <c r="E3" s="17">
+        <v>100</v>
+      </c>
+      <c r="F3" s="17">
+        <v>500</v>
+      </c>
+      <c r="G3" s="17">
+        <v>1000</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="10">
+        <v>304</v>
+      </c>
+      <c r="C4" s="10">
+        <v>305</v>
+      </c>
+      <c r="D4" s="10">
+        <v>304</v>
+      </c>
+      <c r="E4" s="10">
+        <v>304</v>
+      </c>
+      <c r="F4" s="10">
+        <v>304</v>
+      </c>
+      <c r="G4" s="10">
+        <v>304</v>
+      </c>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="10">
+        <v>304</v>
+      </c>
+      <c r="C5" s="10">
+        <v>304</v>
+      </c>
+      <c r="D5" s="10">
+        <v>305</v>
+      </c>
+      <c r="E5" s="10">
+        <v>305</v>
+      </c>
+      <c r="F5" s="10">
+        <v>304</v>
+      </c>
+      <c r="G5" s="10">
+        <v>304</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="10">
+        <v>454</v>
+      </c>
+      <c r="C6" s="10">
+        <v>889</v>
+      </c>
+      <c r="D6" s="10">
+        <v>4417</v>
+      </c>
+      <c r="E6" s="10">
+        <v>8832</v>
+      </c>
+      <c r="F6" s="10">
+        <v>44352</v>
+      </c>
+      <c r="G6" s="10">
+        <v>88778</v>
+      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10">
+        <v>454</v>
+      </c>
+      <c r="C7" s="10">
+        <v>897</v>
+      </c>
+      <c r="D7" s="10">
+        <v>4439</v>
+      </c>
+      <c r="E7" s="10">
+        <v>8920</v>
+      </c>
+      <c r="F7" s="10">
+        <v>46569</v>
+      </c>
+      <c r="G7" s="10">
+        <v>89665</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17">
+        <v>2</v>
+      </c>
+      <c r="C13" s="17">
+        <v>10</v>
+      </c>
+      <c r="D13" s="17">
+        <v>50</v>
+      </c>
+      <c r="E13" s="17">
+        <v>100</v>
+      </c>
+      <c r="F13" s="17">
+        <v>500</v>
+      </c>
+      <c r="G13" s="17">
+        <v>1000</v>
+      </c>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="10">
+        <v>558</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1277</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1923</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1906</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1880</v>
+      </c>
+      <c r="G14" s="10">
+        <v>1958</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="10">
+        <v>559</v>
+      </c>
+      <c r="C15" s="10">
+        <v>1264</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1913</v>
+      </c>
+      <c r="E15" s="10">
+        <v>2017</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1934</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1914</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="10">
+        <v>620</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2200</v>
+      </c>
+      <c r="D16" s="10">
+        <v>10015</v>
+      </c>
+      <c r="E16" s="10">
+        <v>19541</v>
+      </c>
+      <c r="F16" s="10">
+        <v>97079</v>
+      </c>
+      <c r="G16" s="10">
+        <v>198164</v>
+      </c>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10">
+        <v>620</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2222</v>
+      </c>
+      <c r="D17" s="10">
+        <v>10215</v>
+      </c>
+      <c r="E17" s="10">
+        <v>19931</v>
+      </c>
+      <c r="F17" s="10">
+        <v>96108</v>
+      </c>
+      <c r="G17" s="10">
+        <v>200145</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:D12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/results/section2.xlsx
+++ b/results/section2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="58">
   <si>
     <t>Desis</t>
   </si>
@@ -172,6 +172,24 @@
   </si>
   <si>
     <t>1 M</t>
+  </si>
+  <si>
+    <t>1m</t>
+  </si>
+  <si>
+    <t>slices in event</t>
+  </si>
+  <si>
+    <t>tumbling - time based</t>
+  </si>
+  <si>
+    <t>1 ms - 1s</t>
+  </si>
+  <si>
+    <t>events in slice</t>
+  </si>
+  <si>
+    <t>1M - 1</t>
   </si>
 </sst>
 </file>
@@ -201,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -237,11 +255,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -298,6 +340,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -604,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S130"/>
+  <dimension ref="A1:S141"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1"/>
@@ -615,8 +679,8 @@
     <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="22.6328125" style="1" customWidth="1"/>
     <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
     <col min="13" max="13" width="14.6328125" style="1" customWidth="1"/>
@@ -624,23 +688,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
@@ -780,12 +844,12 @@
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
@@ -1022,23 +1086,23 @@
       <c r="S17" s="2"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
@@ -1165,12 +1229,12 @@
       <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="7"/>
@@ -1300,12 +1364,12 @@
       <c r="G32" s="9"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
@@ -1438,24 +1502,24 @@
       <c r="G39" s="9"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="7"/>
@@ -1580,12 +1644,12 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
@@ -1707,12 +1771,12 @@
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="7"/>
@@ -1834,12 +1898,12 @@
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="7"/>
@@ -1969,12 +2033,12 @@
       <c r="G70" s="13"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="18" t="s">
+      <c r="A71" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -2184,7 +2248,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13" t="s">
         <v>37</v>
       </c>
@@ -2213,7 +2277,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
         <v>37</v>
       </c>
@@ -2242,7 +2306,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>40</v>
       </c>
@@ -2268,186 +2332,375 @@
         <v>41</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A92" s="18" t="s">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A86" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="18"/>
-      <c r="H92" s="18"/>
+      <c r="B86" s="21"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+      <c r="I86" s="13"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A87" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="20"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J87" s="13"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A88" s="7"/>
+      <c r="B88" s="10">
+        <v>2</v>
+      </c>
+      <c r="C88" s="10">
+        <v>10</v>
+      </c>
+      <c r="D88" s="10">
+        <v>50</v>
+      </c>
+      <c r="E88" s="10">
+        <v>100</v>
+      </c>
+      <c r="F88" s="10">
+        <v>500</v>
+      </c>
+      <c r="G88" s="10">
+        <v>1000</v>
+      </c>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J88" s="13"/>
+      <c r="K88" s="13"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A89" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C89" s="10">
+        <v>61</v>
+      </c>
+      <c r="D89" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="E89" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="F89" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="G89" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="J89" s="13"/>
+      <c r="K89" s="13"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A90" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B90" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C90" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="D90" s="10">
+        <v>61</v>
+      </c>
+      <c r="E90" s="10">
+        <v>61</v>
+      </c>
+      <c r="F90" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="G90" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="13"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A91" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B91" s="10">
+        <v>90.8</v>
+      </c>
+      <c r="C91" s="10">
+        <v>177.8</v>
+      </c>
+      <c r="D91" s="10">
+        <v>883.4</v>
+      </c>
+      <c r="E91" s="10">
+        <v>1766.4</v>
+      </c>
+      <c r="F91" s="10">
+        <v>8870.4</v>
+      </c>
+      <c r="G91" s="10">
+        <v>17755.599999999999</v>
+      </c>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
+      <c r="K91" s="13"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A92" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" s="10">
+        <v>90.8</v>
+      </c>
+      <c r="C92" s="10">
+        <v>179.4</v>
+      </c>
+      <c r="D92" s="10">
+        <v>887.8</v>
+      </c>
+      <c r="E92" s="10">
+        <v>1784</v>
+      </c>
+      <c r="F92" s="10">
+        <v>9313.7999999999993</v>
+      </c>
+      <c r="G92" s="10">
+        <v>17933</v>
+      </c>
+      <c r="H92" s="13"/>
       <c r="I92" s="13"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A93" s="19" t="s">
+      <c r="J92" s="13"/>
+      <c r="K92" s="13"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
+      <c r="K93" s="13"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A94" s="16"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+      <c r="L94" s="16"/>
+      <c r="M94" s="16"/>
+      <c r="N94" s="16"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A95" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B95" s="21"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="21"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="21"/>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+      <c r="K95" s="16"/>
+      <c r="L95" s="16"/>
+      <c r="M95" s="16"/>
+      <c r="N95" s="16"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A96" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J93" s="13"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A94" s="7"/>
-      <c r="B94" s="10">
+      <c r="B96" s="20"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17"/>
+      <c r="H96" s="16"/>
+      <c r="I96" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J96" s="16"/>
+      <c r="K96" s="16"/>
+      <c r="L96" s="16"/>
+      <c r="M96" s="16"/>
+      <c r="N96" s="16"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A97" s="17"/>
+      <c r="B97" s="17">
         <v>2</v>
       </c>
-      <c r="C94" s="10">
+      <c r="C97" s="17">
         <v>10</v>
       </c>
-      <c r="D94" s="10">
+      <c r="D97" s="17">
         <v>50</v>
       </c>
-      <c r="E94" s="10">
+      <c r="E97" s="17">
         <v>100</v>
       </c>
-      <c r="F94" s="10">
+      <c r="F97" s="17">
         <v>500</v>
       </c>
-      <c r="G94" s="10">
+      <c r="G97" s="17">
         <v>1000</v>
       </c>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13" t="s">
+      <c r="H97" s="16"/>
+      <c r="I97" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="J94" s="13"/>
-      <c r="K94" s="13"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A95" s="7" t="s">
+      <c r="J97" s="16"/>
+      <c r="K97" s="16"/>
+      <c r="L97" s="16"/>
+      <c r="M97" s="16"/>
+      <c r="N97" s="16"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A98" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B95" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C95" s="10">
-        <v>61</v>
-      </c>
-      <c r="D95" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="E95" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="F95" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="G95" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="J95" s="13"/>
-      <c r="K95" s="13"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A96" s="7" t="s">
+      <c r="B98" s="10">
+        <v>111.6</v>
+      </c>
+      <c r="C98" s="10">
+        <v>255.4</v>
+      </c>
+      <c r="D98" s="10">
+        <v>384.6</v>
+      </c>
+      <c r="E98" s="10">
+        <v>381.2</v>
+      </c>
+      <c r="F98" s="10">
+        <v>376</v>
+      </c>
+      <c r="G98" s="10">
+        <v>391.6</v>
+      </c>
+      <c r="H98" s="16"/>
+      <c r="I98" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J98" s="16"/>
+      <c r="K98" s="16"/>
+      <c r="L98" s="16"/>
+      <c r="M98" s="16"/>
+      <c r="N98" s="16"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A99" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B96" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C96" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="D96" s="10">
-        <v>61</v>
-      </c>
-      <c r="E96" s="10">
-        <v>61</v>
-      </c>
-      <c r="F96" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="G96" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13"/>
-      <c r="K96" s="13"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A97" s="7" t="s">
+      <c r="B99" s="10">
+        <v>111.8</v>
+      </c>
+      <c r="C99" s="10">
+        <v>252.8</v>
+      </c>
+      <c r="D99" s="10">
+        <v>382.6</v>
+      </c>
+      <c r="E99" s="10">
+        <v>403.4</v>
+      </c>
+      <c r="F99" s="10">
+        <v>386.8</v>
+      </c>
+      <c r="G99" s="10">
+        <v>382.8</v>
+      </c>
+      <c r="H99" s="16"/>
+      <c r="I99" s="16"/>
+      <c r="J99" s="16"/>
+      <c r="K99" s="16"/>
+      <c r="L99" s="16"/>
+      <c r="M99" s="16"/>
+      <c r="N99" s="16"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A100" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B97" s="10">
-        <v>90.8</v>
-      </c>
-      <c r="C97" s="10">
-        <v>177.8</v>
-      </c>
-      <c r="D97" s="10">
-        <v>883.4</v>
-      </c>
-      <c r="E97" s="10">
-        <v>1766.4</v>
-      </c>
-      <c r="F97" s="10">
-        <v>8870.4</v>
-      </c>
-      <c r="G97" s="10">
-        <v>17755.599999999999</v>
-      </c>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
-      <c r="J97" s="13"/>
-      <c r="K97" s="13"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A98" s="7" t="s">
+      <c r="B100" s="10">
+        <v>124</v>
+      </c>
+      <c r="C100" s="10">
+        <v>440</v>
+      </c>
+      <c r="D100" s="10">
+        <v>2003</v>
+      </c>
+      <c r="E100" s="10">
+        <v>3908.2</v>
+      </c>
+      <c r="F100" s="10">
+        <v>19415.8</v>
+      </c>
+      <c r="G100" s="10">
+        <v>39632.800000000003</v>
+      </c>
+      <c r="H100" s="16"/>
+      <c r="I100" s="16"/>
+      <c r="J100" s="16"/>
+      <c r="K100" s="16"/>
+      <c r="L100" s="16"/>
+      <c r="M100" s="16"/>
+      <c r="N100" s="16"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A101" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B98" s="10">
-        <v>90.8</v>
-      </c>
-      <c r="C98" s="10">
-        <v>179.4</v>
-      </c>
-      <c r="D98" s="10">
-        <v>887.8</v>
-      </c>
-      <c r="E98" s="10">
-        <v>1784</v>
-      </c>
-      <c r="F98" s="10">
-        <v>9313.7999999999993</v>
-      </c>
-      <c r="G98" s="10">
-        <v>17933</v>
-      </c>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13"/>
-      <c r="K98" s="13"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="13"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A101" s="16"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="16"/>
-      <c r="E101" s="16"/>
-      <c r="F101" s="16"/>
-      <c r="G101" s="16"/>
+      <c r="B101" s="10">
+        <v>124</v>
+      </c>
+      <c r="C101" s="10">
+        <v>444.4</v>
+      </c>
+      <c r="D101" s="10">
+        <v>2043</v>
+      </c>
+      <c r="E101" s="10">
+        <v>3986.2</v>
+      </c>
+      <c r="F101" s="10">
+        <v>19221.599999999999</v>
+      </c>
+      <c r="G101" s="10">
+        <v>40029</v>
+      </c>
       <c r="H101" s="16"/>
       <c r="I101" s="16"/>
       <c r="J101" s="16"/>
@@ -2457,16 +2710,14 @@
       <c r="N101" s="16"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A102" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
-      <c r="G102" s="18"/>
-      <c r="H102" s="18"/>
+      <c r="A102" s="16"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
       <c r="I102" s="16"/>
       <c r="J102" s="16"/>
       <c r="K102" s="16"/>
@@ -2475,19 +2726,14 @@
       <c r="N102" s="16"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A103" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="19"/>
-      <c r="E103" s="17"/>
-      <c r="F103" s="17"/>
-      <c r="G103" s="17"/>
+      <c r="A103" s="16"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="16"/>
       <c r="H103" s="16"/>
-      <c r="I103" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="J103" s="16"/>
       <c r="K103" s="16"/>
       <c r="L103" s="16"/>
@@ -2495,29 +2741,15 @@
       <c r="N103" s="16"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A104" s="17"/>
-      <c r="B104" s="17">
-        <v>2</v>
-      </c>
-      <c r="C104" s="17">
-        <v>10</v>
-      </c>
-      <c r="D104" s="17">
-        <v>50</v>
-      </c>
-      <c r="E104" s="17">
-        <v>100</v>
-      </c>
-      <c r="F104" s="17">
-        <v>500</v>
-      </c>
-      <c r="G104" s="17">
-        <v>1000</v>
-      </c>
+      <c r="A104" s="16"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16"/>
       <c r="H104" s="16"/>
-      <c r="I104" s="16" t="s">
-        <v>46</v>
-      </c>
+      <c r="I104" s="16"/>
       <c r="J104" s="16"/>
       <c r="K104" s="16"/>
       <c r="L104" s="16"/>
@@ -2525,31 +2757,17 @@
       <c r="N104" s="16"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A105" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B105" s="10">
-        <v>111.6</v>
-      </c>
-      <c r="C105" s="10">
-        <v>255.4</v>
-      </c>
-      <c r="D105" s="10">
-        <v>384.6</v>
-      </c>
-      <c r="E105" s="10">
-        <v>381.2</v>
-      </c>
-      <c r="F105" s="10">
-        <v>376</v>
-      </c>
-      <c r="G105" s="10">
-        <v>391.6</v>
-      </c>
-      <c r="H105" s="16"/>
-      <c r="I105" s="16" t="s">
-        <v>47</v>
-      </c>
+      <c r="A105" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B105" s="21"/>
+      <c r="C105" s="21"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="21"/>
+      <c r="F105" s="21"/>
+      <c r="G105" s="21"/>
+      <c r="H105" s="21"/>
+      <c r="I105" s="16"/>
       <c r="J105" s="16"/>
       <c r="K105" s="16"/>
       <c r="L105" s="16"/>
@@ -2557,503 +2775,602 @@
       <c r="N105" s="16"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A106" s="17" t="s">
+      <c r="A106" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="20"/>
+      <c r="C106" s="20"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="17"/>
+      <c r="F106" s="17"/>
+      <c r="G106" s="17"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A107" s="17"/>
+      <c r="B107" s="10">
         <v>2</v>
       </c>
-      <c r="B106" s="10">
-        <v>111.8</v>
-      </c>
-      <c r="C106" s="10">
-        <v>252.8</v>
-      </c>
-      <c r="D106" s="10">
-        <v>382.6</v>
-      </c>
-      <c r="E106" s="10">
-        <v>403.4</v>
-      </c>
-      <c r="F106" s="10">
-        <v>386.8</v>
-      </c>
-      <c r="G106" s="10">
-        <v>382.8</v>
-      </c>
-      <c r="H106" s="16"/>
-      <c r="I106" s="16"/>
-      <c r="J106" s="16"/>
-      <c r="K106" s="16"/>
-      <c r="L106" s="16"/>
-      <c r="M106" s="16"/>
-      <c r="N106" s="16"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A107" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B107" s="10">
-        <v>124</v>
-      </c>
       <c r="C107" s="10">
-        <v>440</v>
+        <v>10</v>
       </c>
       <c r="D107" s="10">
-        <v>2003</v>
+        <v>50</v>
       </c>
       <c r="E107" s="10">
-        <v>3908.2</v>
+        <v>100</v>
       </c>
       <c r="F107" s="10">
-        <v>19415.8</v>
+        <v>500</v>
       </c>
       <c r="G107" s="10">
-        <v>39632.800000000003</v>
+        <v>1000</v>
       </c>
       <c r="H107" s="16"/>
-      <c r="I107" s="16"/>
-      <c r="J107" s="16"/>
-      <c r="K107" s="16"/>
-      <c r="L107" s="16"/>
-      <c r="M107" s="16"/>
-      <c r="N107" s="16"/>
+      <c r="I107" s="16" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B108" s="10">
-        <v>124</v>
+        <v>2000000</v>
       </c>
       <c r="C108" s="10">
-        <v>444.4</v>
+        <v>2000000</v>
       </c>
       <c r="D108" s="10">
-        <v>2043</v>
+        <v>2000000</v>
       </c>
       <c r="E108" s="10">
-        <v>3986.2</v>
+        <v>2000000</v>
       </c>
       <c r="F108" s="10">
-        <v>19221.599999999999</v>
+        <v>2000000</v>
       </c>
       <c r="G108" s="10">
-        <v>40029</v>
+        <v>2000000</v>
       </c>
       <c r="H108" s="16"/>
-      <c r="I108" s="16"/>
-      <c r="J108" s="16"/>
-      <c r="K108" s="16"/>
-      <c r="L108" s="16"/>
-      <c r="M108" s="16"/>
-      <c r="N108" s="16"/>
+      <c r="I108" s="16" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A109" s="16"/>
-      <c r="B109" s="16"/>
-      <c r="C109" s="16"/>
-      <c r="D109" s="16"/>
-      <c r="E109" s="16"/>
-      <c r="F109" s="16"/>
-      <c r="G109" s="16"/>
+      <c r="A109" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="C109" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="D109" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="E109" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="F109" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="G109" s="10">
+        <v>3000000</v>
+      </c>
       <c r="H109" s="16"/>
       <c r="I109" s="16"/>
-      <c r="J109" s="16"/>
-      <c r="K109" s="16"/>
-      <c r="L109" s="16"/>
-      <c r="M109" s="16"/>
-      <c r="N109" s="16"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A110" s="16"/>
-      <c r="B110" s="16"/>
-      <c r="C110" s="16"/>
-      <c r="D110" s="16"/>
-      <c r="E110" s="16"/>
-      <c r="F110" s="16"/>
-      <c r="G110" s="16"/>
+      <c r="A110" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B110" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="C110" s="10">
+        <v>15000000</v>
+      </c>
+      <c r="D110" s="10">
+        <v>75000000</v>
+      </c>
+      <c r="E110" s="10">
+        <v>150000000</v>
+      </c>
+      <c r="F110" s="10">
+        <v>750000000</v>
+      </c>
+      <c r="G110" s="10">
+        <v>1500000000</v>
+      </c>
       <c r="H110" s="16"/>
-      <c r="J110" s="16"/>
-      <c r="K110" s="16"/>
-      <c r="L110" s="16"/>
-      <c r="M110" s="16"/>
-      <c r="N110" s="16"/>
+      <c r="I110" s="16"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
-      <c r="D111" s="16"/>
-      <c r="E111" s="16"/>
-      <c r="F111" s="16"/>
-      <c r="G111" s="16"/>
+      <c r="A111" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B111" s="10">
+        <v>3000000</v>
+      </c>
+      <c r="C111" s="10">
+        <v>15000000</v>
+      </c>
+      <c r="D111" s="10">
+        <v>75000000</v>
+      </c>
+      <c r="E111" s="10">
+        <v>150000000</v>
+      </c>
+      <c r="F111" s="10">
+        <v>750000000</v>
+      </c>
+      <c r="G111" s="10">
+        <v>1500000000</v>
+      </c>
       <c r="H111" s="16"/>
       <c r="I111" s="16"/>
-      <c r="J111" s="16"/>
-      <c r="K111" s="16"/>
-      <c r="L111" s="16"/>
-      <c r="M111" s="16"/>
-      <c r="N111" s="16"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="16"/>
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
-      <c r="D112" s="16"/>
-      <c r="E112" s="16"/>
-      <c r="F112" s="16"/>
-      <c r="G112" s="16"/>
-      <c r="H112" s="16"/>
-      <c r="I112" s="16"/>
-      <c r="J112" s="16"/>
-      <c r="K112" s="16"/>
-      <c r="L112" s="16"/>
-      <c r="M112" s="16"/>
-      <c r="N112" s="16"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A113" s="16"/>
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="16"/>
-      <c r="E113" s="16"/>
-      <c r="F113" s="16"/>
-      <c r="G113" s="16"/>
-      <c r="H113" s="16"/>
-      <c r="I113" s="16"/>
-      <c r="J113" s="16"/>
-      <c r="K113" s="16"/>
-      <c r="L113" s="16"/>
-      <c r="M113" s="16"/>
-      <c r="N113" s="16"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A114" s="18" t="s">
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A113" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B114" s="18"/>
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
+      <c r="B113" s="21"/>
+      <c r="C113" s="21"/>
+      <c r="D113" s="21"/>
+      <c r="E113" s="21"/>
+      <c r="F113" s="21"/>
+      <c r="G113" s="21"/>
+      <c r="H113" s="21"/>
+      <c r="I113" s="18"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A114" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="23"/>
+      <c r="C114" s="23"/>
+      <c r="D114" s="24"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19"/>
       <c r="H114" s="18"/>
-      <c r="I114" s="16"/>
-      <c r="J114" s="16"/>
-      <c r="K114" s="16"/>
-      <c r="L114" s="16"/>
-      <c r="M114" s="16"/>
-      <c r="N114" s="16"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A115" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-      <c r="D115" s="19"/>
-      <c r="E115" s="17"/>
-      <c r="F115" s="17"/>
-      <c r="G115" s="17"/>
-      <c r="H115" s="16"/>
-      <c r="I115" s="16" t="s">
+      <c r="I114" s="18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A116" s="17"/>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A115" s="19"/>
+      <c r="B115" s="10">
+        <v>2</v>
+      </c>
+      <c r="C115" s="10">
+        <v>10</v>
+      </c>
+      <c r="D115" s="10">
+        <v>50</v>
+      </c>
+      <c r="E115" s="10">
+        <v>100</v>
+      </c>
+      <c r="F115" s="10">
+        <v>500</v>
+      </c>
+      <c r="G115" s="10">
+        <v>1000</v>
+      </c>
+      <c r="H115" s="18"/>
+      <c r="I115" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A116" s="19" t="s">
+        <v>0</v>
+      </c>
       <c r="B116" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="C116" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="D116" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="E116" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="F116" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G116" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="H116" s="18"/>
+      <c r="I116" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A117" s="19" t="s">
         <v>2</v>
-      </c>
-      <c r="C116" s="10">
-        <v>10</v>
-      </c>
-      <c r="D116" s="10">
-        <v>50</v>
-      </c>
-      <c r="E116" s="10">
-        <v>100</v>
-      </c>
-      <c r="F116" s="10">
-        <v>500</v>
-      </c>
-      <c r="G116" s="10">
-        <v>1000</v>
-      </c>
-      <c r="H116" s="16"/>
-      <c r="I116" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="17" t="s">
-        <v>0</v>
       </c>
       <c r="B117" s="10">
         <v>2000000</v>
       </c>
       <c r="C117" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="D117" s="10">
+        <v>50000000</v>
+      </c>
+      <c r="E117" s="10">
+        <v>100000000</v>
+      </c>
+      <c r="F117" s="10">
+        <v>500000000</v>
+      </c>
+      <c r="G117" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="H117" s="18"/>
+      <c r="I117" s="18"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A118" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" s="10">
         <v>2000000</v>
       </c>
-      <c r="D117" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="E117" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="F117" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="G117" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="H117" s="16"/>
-      <c r="I117" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A118" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B118" s="10">
-        <v>3000000</v>
-      </c>
       <c r="C118" s="10">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="D118" s="10">
-        <v>3000000</v>
+        <v>50000000</v>
       </c>
       <c r="E118" s="10">
-        <v>3000000</v>
+        <v>100000000</v>
       </c>
       <c r="F118" s="10">
-        <v>3000000</v>
+        <v>500000000</v>
       </c>
       <c r="G118" s="10">
-        <v>3000000</v>
+        <v>1000000000</v>
       </c>
       <c r="H118" s="16"/>
       <c r="I118" s="16"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="17" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B119" s="10">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="C119" s="10">
-        <v>15000000</v>
+        <v>10000000</v>
       </c>
       <c r="D119" s="10">
-        <v>75000000</v>
+        <v>50000000</v>
       </c>
       <c r="E119" s="10">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F119" s="10">
-        <v>750000000</v>
+        <v>500000000</v>
       </c>
       <c r="G119" s="10">
-        <v>1500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="H119" s="16"/>
       <c r="I119" s="16"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A120" s="17" t="s">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A124" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B124" s="21"/>
+      <c r="C124" s="21"/>
+      <c r="D124" s="21"/>
+      <c r="E124" s="21"/>
+      <c r="F124" s="21"/>
+      <c r="G124" s="21"/>
+      <c r="H124" s="21"/>
+      <c r="I124" s="18"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A125" s="25"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="25"/>
+      <c r="D125" s="25"/>
+      <c r="E125" s="19"/>
+      <c r="F125" s="19"/>
+      <c r="G125" s="19"/>
+      <c r="H125" s="19"/>
+      <c r="I125" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A126" s="19"/>
+      <c r="B126" s="10">
         <v>1</v>
       </c>
-      <c r="B120" s="10">
-        <v>3000000</v>
-      </c>
-      <c r="C120" s="10">
-        <v>15000000</v>
-      </c>
-      <c r="D120" s="10">
-        <v>75000000</v>
-      </c>
-      <c r="E120" s="10">
-        <v>150000000</v>
-      </c>
-      <c r="F120" s="10">
-        <v>750000000</v>
-      </c>
-      <c r="G120" s="10">
-        <v>1500000000</v>
-      </c>
-      <c r="H120" s="16"/>
-      <c r="I120" s="16"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A121" s="16"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A124" s="18" t="s">
+      <c r="C126" s="10">
+        <v>2</v>
+      </c>
+      <c r="D126" s="10">
+        <v>10</v>
+      </c>
+      <c r="E126" s="10">
         <v>50</v>
       </c>
-      <c r="B124" s="18"/>
-      <c r="C124" s="18"/>
-      <c r="D124" s="18"/>
-      <c r="E124" s="18"/>
-      <c r="F124" s="18"/>
-      <c r="G124" s="18"/>
-      <c r="H124" s="18"/>
-      <c r="I124" s="16"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A125" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B125" s="19"/>
-      <c r="C125" s="19"/>
-      <c r="D125" s="19"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="17"/>
-      <c r="G125" s="17"/>
-      <c r="H125" s="16"/>
-      <c r="I125" s="16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A126" s="17"/>
-      <c r="B126" s="10">
+      <c r="F126" s="10">
+        <v>100</v>
+      </c>
+      <c r="G126" s="10">
+        <v>500</v>
+      </c>
+      <c r="H126" s="10">
+        <v>1000</v>
+      </c>
+      <c r="I126" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A127" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" s="10">
+        <v>32104988.823600002</v>
+      </c>
+      <c r="C127" s="10">
+        <v>31091440.489999998</v>
+      </c>
+      <c r="D127" s="10">
+        <v>28553796.32</v>
+      </c>
+      <c r="E127" s="10">
+        <v>27188459.649999999</v>
+      </c>
+      <c r="F127" s="10">
+        <v>26741444.129999999</v>
+      </c>
+      <c r="G127" s="10">
+        <v>25673297.190000001</v>
+      </c>
+      <c r="H127" s="10">
+        <v>24965849.129999999</v>
+      </c>
+      <c r="I127" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A128" s="18"/>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="18"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="18"/>
+      <c r="G128" s="18"/>
+      <c r="H128" s="18"/>
+      <c r="I128" s="18"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A129" s="18"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="18"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="18"/>
+      <c r="G129" s="18"/>
+      <c r="H129" s="18"/>
+      <c r="I129" s="18"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A130" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B130" s="21"/>
+      <c r="C130" s="21"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="21"/>
+      <c r="F130" s="21"/>
+      <c r="G130" s="21"/>
+      <c r="H130" s="21"/>
+      <c r="I130" s="18"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A131" s="25"/>
+      <c r="B131" s="25"/>
+      <c r="C131" s="25"/>
+      <c r="D131" s="25"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A132" s="19"/>
+      <c r="B132" s="26">
+        <v>1</v>
+      </c>
+      <c r="C132" s="26">
         <v>2</v>
       </c>
-      <c r="C126" s="10">
+      <c r="D132" s="26">
         <v>10</v>
       </c>
-      <c r="D126" s="10">
-        <v>50</v>
-      </c>
-      <c r="E126" s="10">
+      <c r="E132" s="26">
         <v>100</v>
       </c>
-      <c r="F126" s="10">
-        <v>500</v>
-      </c>
-      <c r="G126" s="10">
+      <c r="F132" s="26">
         <v>1000</v>
       </c>
-      <c r="H126" s="16"/>
-      <c r="I126" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A127" s="17" t="s">
+      <c r="G132" s="26">
+        <v>10000</v>
+      </c>
+      <c r="H132" s="26">
+        <v>100000</v>
+      </c>
+      <c r="I132" s="26">
+        <v>1000000</v>
+      </c>
+      <c r="J132" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A133" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B133" s="27">
+        <v>624.2319</v>
+      </c>
+      <c r="C133" s="10">
+        <v>5023.6679999999997</v>
+      </c>
+      <c r="D133" s="10">
+        <v>142078.48000000001</v>
+      </c>
+      <c r="E133" s="10">
+        <v>5260162.8600000003</v>
+      </c>
+      <c r="F133" s="10">
+        <v>11496597.6</v>
+      </c>
+      <c r="G133" s="10">
+        <v>14544166.01</v>
+      </c>
+      <c r="H133" s="10">
+        <v>15479305.59</v>
+      </c>
+      <c r="I133" s="27">
+        <v>15852103.43</v>
+      </c>
+      <c r="J133" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B134" s="1">
         <v>1000000</v>
       </c>
-      <c r="C127" s="10">
-        <v>1000000</v>
-      </c>
-      <c r="D127" s="10">
-        <v>1000000</v>
-      </c>
-      <c r="E127" s="10">
-        <v>1000000</v>
-      </c>
-      <c r="F127" s="10">
-        <v>1000000</v>
-      </c>
-      <c r="G127" s="10">
-        <v>1000000</v>
-      </c>
-      <c r="H127" s="16"/>
-      <c r="I127" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A128" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B128" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="C128" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="D128" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="E128" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="F128" s="10">
-        <v>500000000</v>
-      </c>
-      <c r="G128" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="H128" s="16"/>
-      <c r="I128" s="16"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A129" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B129" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="C129" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="D129" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="E129" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="F129" s="10">
-        <v>500000000</v>
-      </c>
-      <c r="G129" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="H129" s="16"/>
-      <c r="I129" s="16"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A130" s="17" t="s">
+      <c r="C134" s="9">
+        <v>500000</v>
+      </c>
+      <c r="D134" s="9">
+        <v>100000</v>
+      </c>
+      <c r="E134" s="9">
+        <v>10000</v>
+      </c>
+      <c r="F134" s="9">
+        <v>1000</v>
+      </c>
+      <c r="G134" s="9">
+        <v>100</v>
+      </c>
+      <c r="H134" s="9">
+        <v>10</v>
+      </c>
+      <c r="I134" s="9">
         <v>1</v>
       </c>
-      <c r="B130" s="10">
-        <v>2000000</v>
-      </c>
-      <c r="C130" s="10">
-        <v>10000000</v>
-      </c>
-      <c r="D130" s="10">
-        <v>50000000</v>
-      </c>
-      <c r="E130" s="10">
-        <v>100000000</v>
-      </c>
-      <c r="F130" s="10">
-        <v>500000000</v>
-      </c>
-      <c r="G130" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="H130" s="16"/>
-      <c r="I130" s="16"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A137" s="18"/>
+      <c r="B137" s="18"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
+      <c r="E137" s="18"/>
+      <c r="F137" s="18"/>
+      <c r="G137" s="18"/>
+      <c r="H137" s="18"/>
+      <c r="I137" s="18"/>
+      <c r="J137" s="18"/>
+      <c r="K137" s="18"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A138" s="18"/>
+      <c r="B138" s="18"/>
+      <c r="C138" s="18"/>
+      <c r="D138" s="18"/>
+      <c r="E138" s="18"/>
+      <c r="F138" s="18"/>
+      <c r="G138" s="18"/>
+      <c r="H138" s="18"/>
+      <c r="I138" s="18"/>
+      <c r="J138" s="18"/>
+      <c r="K138" s="18"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A139" s="18"/>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18"/>
+      <c r="F139" s="18"/>
+      <c r="G139" s="18"/>
+      <c r="H139" s="18"/>
+      <c r="I139" s="18"/>
+      <c r="J139" s="18"/>
+      <c r="K139" s="18"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A140" s="18"/>
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
+      <c r="G140" s="18"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="18"/>
+      <c r="J140" s="18"/>
+      <c r="K140" s="18"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A141" s="18"/>
+      <c r="B141" s="18"/>
+      <c r="C141" s="18"/>
+      <c r="D141" s="18"/>
+      <c r="E141" s="18"/>
+      <c r="F141" s="18"/>
+      <c r="G141" s="18"/>
+      <c r="H141" s="18"/>
+      <c r="I141" s="18"/>
+      <c r="J141" s="18"/>
+      <c r="K141" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A114:H114"/>
-    <mergeCell ref="A115:D115"/>
+  <mergeCells count="23">
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A113:H113"/>
     <mergeCell ref="A124:H124"/>
-    <mergeCell ref="A125:D125"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A43:D43"/>
@@ -3063,8 +3380,9 @@
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A93:D93"/>
-    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A105:H105"/>
+    <mergeCell ref="A106:D106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3077,25 +3395,25 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
       <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
@@ -3265,25 +3583,25 @@
       <c r="I10" s="16"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
       <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
